--- a/automation_engine/modules/aoc4/excel/ANNFIL COMMONERROR.xlsx
+++ b/automation_engine/modules/aoc4/excel/ANNFIL COMMONERROR.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6c9e8928e28eb49/process/Tech automation/sample data to arca/Use case/Common Error/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{E116BEEF-F543-4AD1-94E4-953A97DAF1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4869699-092F-46BE-8D29-B4BC00AAACAD}"/>
+  <xr:revisionPtr revIDLastSave="180" documentId="13_ncr:1_{E116BEEF-F543-4AD1-94E4-953A97DAF1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD33AD8C-0E15-42BA-A0A1-E9E93E2CCD28}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{251BD1AF-8FB9-4BCC-B3DC-C8E6E40C2030}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{251BD1AF-8FB9-4BCC-B3DC-C8E6E40C2030}"/>
   </bookViews>
   <sheets>
     <sheet name="Common Error" sheetId="1" r:id="rId1"/>
-    <sheet name="compliance sheet with template" sheetId="4" r:id="rId2"/>
-    <sheet name="compliance sheet" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="RPT and loans to Director" sheetId="2" r:id="rId4"/>
-    <sheet name="Freezing the input" sheetId="5" r:id="rId5"/>
+    <sheet name="compliance sheet" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="compliance for Private " sheetId="4" r:id="rId3"/>
+    <sheet name="compliance for public" sheetId="7" r:id="rId4"/>
+    <sheet name="RPT and loans to Director" sheetId="2" r:id="rId5"/>
+    <sheet name="Freezing the input" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="312">
   <si>
     <t>S.No</t>
   </si>
@@ -51,6 +52,9 @@
     <t>SOURCE</t>
   </si>
   <si>
+    <t>Yes/No/NA</t>
+  </si>
+  <si>
     <t>Comments</t>
   </si>
   <si>
@@ -58,7 +62,7 @@
   </si>
   <si>
     <t xml:space="preserve">Whether audit report has the following fields 
-a) Opinion of the Auditor
+a) Opinion of the Auditor 
 b) Basis of Opinion
 c) Emphasis of matter
 d) Key Audit Matters
@@ -74,6 +78,9 @@
     <t>Auditors report</t>
   </si>
   <si>
+    <t xml:space="preserve">whether CARO/Companies (Auditor's Report) Order is as per  format given in Jamku&gt;Services&gt;ANNUAL FILING &gt;SAMPLE CARO </t>
+  </si>
+  <si>
     <t xml:space="preserve">whether Schedule III is as per format in Jamku&gt;Services&gt;ANNUAL FILING &gt;SAMPLE SCHEDULE III </t>
   </si>
   <si>
@@ -249,6 +256,9 @@
     <t>Source</t>
   </si>
   <si>
+    <t>Key words</t>
+  </si>
+  <si>
     <t>Financial Particulars</t>
   </si>
   <si>
@@ -264,7 +274,10 @@
     <t>Should not be Subsidiary or Holding Company</t>
   </si>
   <si>
-    <t>Balance sheet</t>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance Sheet, Equity → paid.?up capital, paid.?up share capital, subscribed and paid.?up, equity share capital and Preference  → paid.?up capital, paid.?up share capital, subscribed and paid.?up, equity share capital </t>
   </si>
   <si>
     <t>Paidup capital</t>
@@ -273,6 +286,9 @@
     <t>Subsidiary Company</t>
   </si>
   <si>
+    <t>Balance Sheet, Equity → reserves and surplus, reserves &amp; surplus, other equity, retained earnings</t>
+  </si>
+  <si>
     <t>Reserves and Surplus</t>
   </si>
   <si>
@@ -282,18 +298,27 @@
     <t>Result</t>
   </si>
   <si>
-    <t>Borrowings</t>
+    <t>Balance Sheet, Liabilities → borrowings, long.?term borrowings, short.?term borrowings, secured loans, unsecured loans</t>
+  </si>
+  <si>
+    <t>Total Borrowings</t>
   </si>
   <si>
     <t>Not a Holding or subsidiary Company</t>
   </si>
   <si>
+    <t>Balance Sheet, Assets / Related Party Note → loans and advances to directors, due from directors, loans to related parties, advance to KMP</t>
+  </si>
+  <si>
     <t>Loangiven by Company to Directors or Director related entities (assets)</t>
   </si>
   <si>
     <t>compny</t>
   </si>
   <si>
+    <t>Balance Sheet, Assets → loans and advances (assets), loans given, inter.?corporate deposits given, ICD given</t>
+  </si>
+  <si>
     <t>Loans given by Company (assets)</t>
   </si>
   <si>
@@ -306,6 +331,9 @@
     <t xml:space="preserve">Applicability </t>
   </si>
   <si>
+    <t>Balance Sheet, Assets → investments, non.?current investments, current investments, investment in subsidiaries/associates</t>
+  </si>
+  <si>
     <t>Investments made by Company (assets)</t>
   </si>
   <si>
@@ -324,6 +352,9 @@
     <t>unlisted</t>
   </si>
   <si>
+    <t>Notes, Contingent Liabilities → corporate guarantee, guarantees given, contingent liabilities.*guarantee</t>
+  </si>
+  <si>
     <t>Corporate Guarantees given by Company</t>
   </si>
   <si>
@@ -339,7 +370,7 @@
     <t>pvt</t>
   </si>
   <si>
-    <t>Related party transaction</t>
+    <t>Balance Sheet, Liabilities / Related Party Note → loan from directors, unsecured loan from director, due to directors, loans from relatives of directors</t>
   </si>
   <si>
     <t>Loan from Directors or their relatives (Liabilities)</t>
@@ -357,12 +388,18 @@
     <t>Other than small</t>
   </si>
   <si>
+    <t>Balance Sheet, Liabilities → loan from shareholders, unsecured loan from shareholder, ICD from shareholder</t>
+  </si>
+  <si>
     <t>Loan from Shareholders (Liabilities)</t>
   </si>
   <si>
     <t>PUC + RS not more than 1 Cr</t>
   </si>
   <si>
+    <t>Balance Sheet, Liabilities → secured loan, term loan (secured), loan against hypothecation, secured borrowings</t>
+  </si>
+  <si>
     <t>Secured Loan</t>
   </si>
   <si>
@@ -375,13 +412,19 @@
     <t>Total revenue not exceeding 10 Cr</t>
   </si>
   <si>
+    <t>Balance Sheet, Liabilities / Notes → advance from customers, security deposit received, advance received, customer advances</t>
+  </si>
+  <si>
     <t>Dues to MSME</t>
   </si>
   <si>
+    <t>Capital + reserves &amp; surplus</t>
+  </si>
+  <si>
     <t>Networth</t>
   </si>
   <si>
-    <t>P&amp;L - Revenue from operations</t>
+    <t>P&amp;L → revenue from operations, total turnover, sales turnover, gross turnover</t>
   </si>
   <si>
     <t>Turnover</t>
@@ -393,18 +436,24 @@
     <t>Year 3</t>
   </si>
   <si>
-    <t>P&amp;L</t>
+    <t>P&amp;L → total revenue, total income, revenue and other income</t>
   </si>
   <si>
     <t>Total Revenue</t>
   </si>
   <si>
+    <t>P&amp;L → profit before tax, PBT, profit/(loss) before tax</t>
+  </si>
+  <si>
     <t>Profit Before Tax</t>
   </si>
   <si>
     <t>Corporate Social Responsibility</t>
   </si>
   <si>
+    <t>RemunerationRelated Party Note / Notes to Accounts → annual remuneration, remuneration paid to directors, managerial remuneration (then compute: annual ÷ 12)</t>
+  </si>
+  <si>
     <t>ED / WTD - 1 Monthly Remuneration</t>
   </si>
   <si>
@@ -414,6 +463,9 @@
     <t>Net worth of Rs.500 crore or more; OR</t>
   </si>
   <si>
+    <t>Notes, Revenue breakup → export sales, export turnover, revenue from export, FOB value of exports</t>
+  </si>
+  <si>
     <t>Exprt</t>
   </si>
   <si>
@@ -426,22 +478,28 @@
     <t>ED / WTD - 5 Monthly Remuneration</t>
   </si>
   <si>
+    <t>Related Party Note / Notes to Accounts → sitting fees, fees to directors, director sitting fee</t>
+  </si>
+  <si>
     <t>Sitting Fees to Directors</t>
   </si>
   <si>
-    <t>Balance sheet - Share capital notes</t>
+    <t>Notes, Share Capital breakup → corporate shareholder, holding more than 10%, shareholding pattern</t>
   </si>
   <si>
     <t>Number of Bodies Corporate Shareholder holding more than 10%</t>
   </si>
   <si>
+    <t>Notes, Company Overview / Related Party → holding company, subsidiary company, is a subsidiary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Is the Company a Holding or a Subsidiary Company </t>
   </si>
   <si>
     <t>Rotation of Auditors</t>
   </si>
   <si>
-    <t>Financials</t>
+    <t>Notes, Related Party Disclosures → associate company, joint venture, related party as per Ind AS 24</t>
   </si>
   <si>
     <t>Is the Company a Holding, Subsidiary or Associate of IND AS applicable Companies</t>
@@ -532,6 +590,9 @@
     <t>AOC 1</t>
   </si>
   <si>
+    <t>=IF($C$31=$H$9,C58"Applicable, Check AOC 1 is annexed with Board's report","Not Applicable")</t>
+  </si>
+  <si>
     <t>AOC 2</t>
   </si>
   <si>
@@ -617,9 +678,90 @@
     <t>Don’t have loans, investments, guaratnees</t>
   </si>
   <si>
+    <t xml:space="preserve">Name of the Company : </t>
+  </si>
+  <si>
+    <t>Women Director</t>
+  </si>
+  <si>
+    <t>TO less than 20 Cr and PUC less than 2 Cr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Public Company  having PSC – 100 Cr or more (or) T.O of 300 Cr or more </t>
+  </si>
+  <si>
+    <t>Independent Director / AC / NRC</t>
+  </si>
+  <si>
+    <t>Borrowings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Company having PSC- 10 Cr or more (or) T.O 100 Cr or more (or) Aggregate O/S Loans, Deb, deposits &gt;50 Cr </t>
+  </si>
+  <si>
+    <t>IND AS</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>Export</t>
+  </si>
+  <si>
+    <t>Public Company - PUC more than 10 Cr</t>
+  </si>
+  <si>
+    <t>All Companies - Borrowings more than Rs 50 Cr</t>
+  </si>
+  <si>
+    <t>ED / WTD - 3 Monthly Remuneration</t>
+  </si>
+  <si>
+    <t>ED / WTD - 4 Monthly Remuneration</t>
+  </si>
+  <si>
+    <t>Accounting Standard</t>
+  </si>
+  <si>
+    <t>IND AS Applicability</t>
+  </si>
+  <si>
+    <t>No it is not a small company</t>
+  </si>
+  <si>
+    <t>CS appointment</t>
+  </si>
+  <si>
+    <t>Independent Director</t>
+  </si>
+  <si>
+    <t>Audit Committee</t>
+  </si>
+  <si>
+    <t>Nomination and Remuneration Committee</t>
+  </si>
+  <si>
+    <t>PUC 50 Cr or more</t>
+  </si>
+  <si>
+    <t>Annual Board Evaluation</t>
+  </si>
+  <si>
+    <t>Public Company  PUC – 50 Cr or  more;</t>
+  </si>
+  <si>
+    <t>Public Company T.O of 250 Crore or more;</t>
+  </si>
+  <si>
+    <t>Any Company - To appoint CS - PUC 5 Cr or more</t>
+  </si>
+  <si>
     <t>SECTION 188</t>
   </si>
   <si>
+    <t>SOURCE : Notes to Accounts - Related party transaction</t>
+  </si>
+  <si>
     <t>RELATED PARTY TRANSACTION</t>
   </si>
   <si>
@@ -629,6 +771,12 @@
     <t>Based on last year T.O and N.W</t>
   </si>
   <si>
+    <t>Turnover @ 10% as per previous year</t>
+  </si>
+  <si>
+    <t>Networth @ 10% as per previous year</t>
+  </si>
+  <si>
     <t>If there is Material Transaction, then AOC 2 is applicable. If the transaction is not material AOC 2 is Not applicable</t>
   </si>
   <si>
@@ -647,10 +795,16 @@
     <t>Actuals</t>
   </si>
   <si>
+    <t>Is this a material transaction (actuals &gt; limits) - Yes</t>
+  </si>
+  <si>
     <t>Sale of Goods</t>
   </si>
   <si>
     <t xml:space="preserve">10 % or more of turnover </t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
   <si>
     <t>Purchase or supply of goods or materials directly or through appointment of agents</t>
@@ -839,12 +993,6 @@
     <t>If exceeding limit, to mention in MGT 8 &amp; prior approval/ratification in next AGM/EGM</t>
   </si>
   <si>
-    <t xml:space="preserve">whether CARO/Companies (Auditor's Report) Order is as per  format given in Jamku&gt;Services&gt;ANNUAL FILING &gt;SAMPLE CARO </t>
-  </si>
-  <si>
-    <t>Yes/No/NA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Input for the Common Error </t>
   </si>
   <si>
@@ -866,19 +1014,10 @@
     <t>Input for the Compliance sheet</t>
   </si>
   <si>
-    <t>SOURCE : Notes to Accounts - Related party transaction</t>
-  </si>
-  <si>
-    <t>Turnover @ 10% as per previous year</t>
-  </si>
-  <si>
-    <t>Networth @ 10% as per previous year</t>
-  </si>
-  <si>
-    <t>Is this a material transaction (actuals &gt; limits) - Yes</t>
-  </si>
-  <si>
-    <t>no</t>
+    <t xml:space="preserve">Balance sheet </t>
+  </si>
+  <si>
+    <t>Boards report</t>
   </si>
 </sst>
 </file>
@@ -893,7 +1032,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,7 +1182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1086,8 +1225,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="24">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1394,6 +1539,32 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1406,7 +1577,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1542,9 +1713,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1610,15 +1778,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="15" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1632,13 +1856,24 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1647,11 +1882,171 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 11 2 2" xfId="4" xr:uid="{B8FEC127-A2BE-402A-A978-666028E78C1B}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="33">
     <dxf>
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1835,10 +2230,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2158,19 +2549,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{253CE8AB-4F99-47A3-8D43-47FF2AC2EF71}">
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="77" style="35" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="41.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="29" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="1"/>
+    <col min="6" max="6" width="22.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="47.85546875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="11" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="11" customFormat="1" ht="36.75" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2181,499 +2574,499 @@
         <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>253</v>
+        <v>3</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="11" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="11" customFormat="1" ht="187.15">
       <c r="A2" s="13">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="9"/>
       <c r="E2" s="9"/>
       <c r="F2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="H2" s="124"/>
+    </row>
+    <row r="3" spans="1:8" s="11" customFormat="1" ht="31.15">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>252</v>
+        <v>8</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="5"/>
       <c r="F3" s="8"/>
     </row>
-    <row r="4" spans="1:6" s="11" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" s="11" customFormat="1" ht="31.15">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="31.15">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
     </row>
-    <row r="6" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="31.15">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="7"/>
       <c r="B8" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
     </row>
-    <row r="9" spans="1:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="26.45" customHeight="1">
       <c r="A9" s="7"/>
       <c r="B9" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
     </row>
-    <row r="10" spans="1:6" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="42.6" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
     </row>
-    <row r="11" spans="1:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="37.15" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
     </row>
-    <row r="12" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="31.15">
       <c r="A12" s="7"/>
       <c r="B12" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="31.15">
       <c r="A13" s="7"/>
       <c r="B13" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:6" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="26.45" customHeight="1">
       <c r="A14" s="7">
         <v>7</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="A15" s="7">
         <v>8</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="A16" s="7">
         <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="31.15">
       <c r="A17" s="7">
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="A18" s="7">
         <v>11</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6">
       <c r="A19" s="7">
         <v>12</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="46.9">
       <c r="A20" s="7">
         <v>13</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6">
       <c r="A21" s="7">
         <v>14</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="31.15">
       <c r="A22" s="7">
         <v>15</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="31.15">
       <c r="A23" s="7"/>
       <c r="B23" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="31.15">
       <c r="A24" s="7"/>
       <c r="B24" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="31.15">
       <c r="A25" s="7"/>
       <c r="B25" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6">
       <c r="A26" s="7"/>
       <c r="B26" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="31.15">
       <c r="A27" s="7"/>
       <c r="B27" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="31.15">
       <c r="A28" s="7"/>
       <c r="B28" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="31.15">
       <c r="A29" s="7">
         <v>16</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="8"/>
+        <v>44</v>
+      </c>
+      <c r="C29" s="6"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6">
       <c r="A30" s="7"/>
       <c r="B30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="6"/>
+        <v>45</v>
+      </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6">
       <c r="A31" s="7"/>
       <c r="B31" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6">
       <c r="A32" s="7"/>
       <c r="B32" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6">
       <c r="A33" s="7"/>
       <c r="B33" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6">
       <c r="A34" s="7"/>
       <c r="B34" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6">
       <c r="A35" s="7"/>
       <c r="B35" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
     </row>
-    <row r="36" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="31.15">
       <c r="A36" s="7"/>
       <c r="B36" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
     </row>
-    <row r="37" spans="1:6" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="46.9">
       <c r="A37" s="7"/>
       <c r="B37" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
     </row>
-    <row r="38" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="31.15">
       <c r="A38" s="5">
         <v>17</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
     </row>
-    <row r="39" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="31.15">
       <c r="A39" s="5">
         <v>18</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B40" s="111"/>
+    <row r="40" spans="1:6">
+      <c r="B40" s="110"/>
       <c r="C40" s="32"/>
       <c r="D40" s="32"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B41" s="112"/>
+    <row r="41" spans="1:6">
+      <c r="B41" s="111"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="16" priority="2" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="32" priority="2" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:D18">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2683,1837 +3076,3761 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E89D1D-3350-4790-B327-21F1F8282FE5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2528822E-8F8D-4F2A-A74B-921C06C3ADD0}">
-  <dimension ref="A1:X97"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Y97"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.33203125" style="35" customWidth="1"/>
-    <col min="4" max="4" width="34.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.33203125" style="35" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16" style="1" customWidth="1"/>
-    <col min="9" max="9" width="3.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="49.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="24" style="1" customWidth="1"/>
-    <col min="13" max="16" width="9.33203125" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.33203125" style="1"/>
+    <col min="1" max="1" width="16" style="1" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" style="35" customWidth="1"/>
+    <col min="3" max="3" width="54.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" style="35" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" style="35" customWidth="1"/>
+    <col min="7" max="7" width="34.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="43.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="1" customWidth="1"/>
+    <col min="14" max="17" width="9.28515625" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="J1" s="115" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-    </row>
-    <row r="3" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J4" s="36"/>
-      <c r="K4" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="L4" s="38" t="s">
+    <row r="1" spans="1:25">
+      <c r="K1" s="139" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="116" t="s">
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+    </row>
+    <row r="3" spans="1:25" ht="16.149999999999999" thickBot="1"/>
+    <row r="4" spans="1:25" ht="16.149999999999999" thickBot="1">
+      <c r="K4" s="36"/>
+      <c r="L4" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="J5" s="39" t="s">
+      <c r="M4" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="40" t="s">
+    </row>
+    <row r="5" spans="1:25" ht="16.149999999999999" thickBot="1">
+      <c r="C5" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="41"/>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B6" s="42"/>
-      <c r="C6" s="117" t="s">
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="K5" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117" t="s">
+      <c r="L5" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="118"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="44" t="s">
+      <c r="M5" s="41"/>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="C6" s="42"/>
+      <c r="D6" s="140" t="s">
         <v>62</v>
       </c>
-      <c r="J6" s="45" t="s">
+      <c r="E6" s="140"/>
+      <c r="F6" s="140" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="46" t="str">
-        <f>IF((AND($C$8&lt;100000000,$C$21&lt;1000000000)), $H$7, $H$6)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L6" s="47"/>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="114" t="s">
+      <c r="G6" s="141"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="K6" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="L6" s="46" t="str">
+        <f>IF((AND($D$8&lt;100000000,$D$21&lt;1000000000)), $I$7, $I$6)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M6" s="47"/>
+    </row>
+    <row r="7" spans="1:25">
+      <c r="A7" s="112" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="C7" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="44" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="50" t="str">
+        <f>IF(OR($D$31=$I$8,$D$31=$I$9),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M7" s="47"/>
+    </row>
+    <row r="8" spans="1:25" ht="93.6">
+      <c r="A8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="127"/>
+      <c r="E8" s="53">
+        <f>D8/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="131"/>
+      <c r="G8" s="54">
+        <f t="shared" ref="G8:G16" si="0">F8/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="45"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="47"/>
+    </row>
+    <row r="9" spans="1:25" ht="43.15">
+      <c r="A9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="125" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="127"/>
+      <c r="E9" s="53">
+        <f t="shared" ref="E9:E30" si="1">D9/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="131"/>
+      <c r="G9" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="L9" s="57" t="str">
+        <f>IF(OR($L$6=$I$6,$L$7=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M9" s="58"/>
+    </row>
+    <row r="10" spans="1:25" ht="43.15">
+      <c r="A10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="125" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="127"/>
+      <c r="E10" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="131"/>
+      <c r="G10" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="59"/>
+      <c r="L10" s="60"/>
+      <c r="M10" s="61"/>
+    </row>
+    <row r="11" spans="1:25" ht="62.45">
+      <c r="A11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="127"/>
+      <c r="E11" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="131"/>
+      <c r="G11" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="62"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="64"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="46.5">
+      <c r="A12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="127"/>
+      <c r="E12" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="131"/>
+      <c r="G12" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="65">
+        <f>$F$20*0.6</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" s="41"/>
+    </row>
+    <row r="13" spans="1:25" ht="61.5">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="127"/>
+      <c r="E13" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="131"/>
+      <c r="G13" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="65">
+        <f>$F$9</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M13" s="47"/>
+      <c r="T13" s="67" t="s">
+        <v>97</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="46.9">
+      <c r="A14" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="127"/>
+      <c r="E14" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="131"/>
+      <c r="G14" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="65">
+        <f>MAX($I$12,$I$13)</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="46" t="str">
+        <f>L9</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M14" s="47"/>
+      <c r="T14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="V14" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="W14" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="57.6">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="127"/>
+      <c r="E15" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="131"/>
+      <c r="G15" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="K15" s="66" t="s">
+        <v>107</v>
+      </c>
+      <c r="L15" s="46" t="str">
+        <f>IF((AND($D$8&lt;40000000,$D$21&lt;400000000)), $I$7, $I$6)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M15" s="47"/>
+      <c r="W15" s="69" t="s">
+        <v>108</v>
+      </c>
+      <c r="X15" s="70" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y15" s="71" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="43.15">
+      <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="125" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" s="127"/>
+      <c r="E16" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="131"/>
+      <c r="G16" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="K16" s="72" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="46" t="str">
+        <f>IF(($D$8+$D$9)&gt;10000000,$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M16" s="47"/>
+    </row>
+    <row r="17" spans="1:13" ht="43.15">
+      <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="125" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="66" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="127"/>
+      <c r="E17" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="132"/>
+      <c r="G17" s="54">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="K17" s="72" t="s">
+        <v>116</v>
+      </c>
+      <c r="L17" s="46" t="str">
+        <f>IF($D$10&gt;10000000, $I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M17" s="47"/>
+    </row>
+    <row r="18" spans="1:13" ht="31.15">
+      <c r="A18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="D18" s="127"/>
+      <c r="E18" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="132"/>
+      <c r="G18" s="54">
+        <f t="shared" ref="G18:G29" si="2">F18/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="K18" s="72" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="46" t="str">
+        <f>IF($D$22&gt;100000000,$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M18" s="47"/>
+    </row>
+    <row r="19" spans="1:13" ht="43.15">
+      <c r="A19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="125" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="128"/>
+      <c r="E19" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="132"/>
+      <c r="G19" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="K19" s="72"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="47"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="B20" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="75" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="127">
+        <f>+D8+D9</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="53">
+        <f>D20/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="131">
+        <f>+F8+F9</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="47"/>
+    </row>
+    <row r="21" spans="1:13" ht="28.9">
+      <c r="A21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="125" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="127"/>
+      <c r="E21" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="131"/>
+      <c r="G21" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="K21" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="57" t="str">
+        <f>IF(OR(L13=$I$6,L14=$I$6,L16=$I$6,L17=$I$6,L18=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M21" s="58"/>
+    </row>
+    <row r="22" spans="1:13" ht="28.9">
+      <c r="A22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="125" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="D22" s="127"/>
+      <c r="E22" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="131"/>
+      <c r="G22" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="133"/>
+      <c r="I22" s="133"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="81"/>
+    </row>
+    <row r="23" spans="1:13" ht="28.9">
+      <c r="A23" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="125" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="127"/>
+      <c r="E23" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="131"/>
+      <c r="G23" s="54">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="82" t="s">
+        <v>131</v>
+      </c>
+      <c r="L23" s="43"/>
+      <c r="M23" s="41"/>
+    </row>
+    <row r="24" spans="1:13" ht="57.6">
+      <c r="A24" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="125" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="129"/>
+      <c r="E24" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="83"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="47"/>
+    </row>
+    <row r="25" spans="1:13" ht="57.6">
+      <c r="A25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="125" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" s="130"/>
+      <c r="E25" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="84" t="s">
+        <v>135</v>
+      </c>
+      <c r="L25" s="46" t="str">
+        <f>IF($D$20&gt;=5000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M25" s="85" t="str">
+        <f>IF($F$20&gt;=5000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="43.15">
+      <c r="A26" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="125" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="130"/>
+      <c r="E26" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="84" t="s">
+        <v>138</v>
+      </c>
+      <c r="L26" s="46" t="str">
+        <f>IF($D$21&gt;=10000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M26" s="85" t="str">
+        <f>IF($F$21&gt;=10000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="43.15">
+      <c r="A27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="125" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="130"/>
+      <c r="E27" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="84" t="s">
+        <v>139</v>
+      </c>
+      <c r="L27" s="46" t="str">
+        <f>IF($D$23&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M27" s="85" t="str">
+        <f>IF($F$23&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="57.6">
+      <c r="A28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B28" s="125" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="130"/>
+      <c r="E28" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="84"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="85"/>
+    </row>
+    <row r="29" spans="1:13" ht="28.9">
+      <c r="A29" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="125" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="130"/>
+      <c r="E29" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="6"/>
+      <c r="G29" s="47">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="L29" s="57" t="str">
+        <f>IF(OR($L$25=$I$6,$L$26=$I$6,$L$27=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M29" s="87" t="str">
+        <f>IF(OR($M$25=$I$6,$M$26=$I$6,$M$27=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="43.15">
+      <c r="A30" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="125" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="66" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="128"/>
+      <c r="E30" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30" s="54">
+        <f>F30/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="79"/>
+      <c r="L30" s="80"/>
+      <c r="M30" s="81"/>
+    </row>
+    <row r="31" spans="1:13" ht="43.5">
+      <c r="A31" s="135" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="136" t="s">
+        <v>145</v>
+      </c>
+      <c r="C31" s="137" t="s">
+        <v>146</v>
+      </c>
+      <c r="D31" s="138" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="47"/>
+      <c r="K31" s="88" t="s">
+        <v>147</v>
+      </c>
+      <c r="L31" s="43"/>
+      <c r="M31" s="41"/>
+    </row>
+    <row r="32" spans="1:13" ht="43.15">
+      <c r="A32" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="125" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="K32" s="84" t="s">
+        <v>150</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M32" s="47"/>
+    </row>
+    <row r="33" spans="1:13" ht="18.600000000000001" thickBot="1">
+      <c r="D33" s="142" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="142"/>
+      <c r="F33" s="143" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="143"/>
+      <c r="K33" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="L33" s="46" t="str">
+        <f>IF($D$8&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M33" s="47"/>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="112" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="B34" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7" s="50" t="str">
-        <f>IF(OR($C$31=$H$8,$C$31=$H$9),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L7" s="47"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="51" t="s">
+      <c r="C34" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="D34" s="89" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" s="89" t="s">
+        <v>61</v>
+      </c>
+      <c r="G34" s="90" t="s">
+        <v>154</v>
+      </c>
+      <c r="K34" s="84"/>
+      <c r="L34" s="46"/>
+      <c r="M34" s="47"/>
+    </row>
+    <row r="35" spans="1:13" ht="16.149999999999999" thickBot="1">
+      <c r="C35" s="91" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="92" t="str">
+        <f>IF((OR($L$9=$I$6,$L$9=$I$6)), "No, It is not a Small Company", "Yes, It is a Small Company")</f>
+        <v>Yes, It is a Small Company</v>
+      </c>
+      <c r="E35" s="93"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="94"/>
+      <c r="K35" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="L35" s="57" t="str">
+        <f>IF(OR($L$32=$I$6,$L$33=$I$6,),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M35" s="58"/>
+    </row>
+    <row r="36" spans="1:13" ht="15.75">
+      <c r="C36" s="45" t="str">
+        <f>K12</f>
+        <v>CARO</v>
+      </c>
+      <c r="D36" s="6" t="str">
+        <f>$L$21</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="54"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="80"/>
+      <c r="M36" s="81"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="C37" s="45" t="str">
+        <f>K31</f>
+        <v>Rotation of Auditors</v>
+      </c>
+      <c r="D37" s="6" t="str">
+        <f>$L$35</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="54"/>
+      <c r="K37" s="95" t="s">
+        <v>156</v>
+      </c>
+      <c r="L37" s="96"/>
+      <c r="M37" s="41"/>
+    </row>
+    <row r="38" spans="1:13" ht="15.75">
+      <c r="C38" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" s="97" t="str">
+        <f>IF(OR($D$32=$I$6,$D$20&gt;=2500000000,),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="54"/>
+      <c r="K38" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="M38" s="47"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="C39" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="6" t="str">
+        <f>$L$42</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="54"/>
+      <c r="K39" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="L39" s="46" t="str">
+        <f>IF($D$8&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M39" s="47"/>
+    </row>
+    <row r="40" spans="1:13" ht="15.75">
+      <c r="C40" s="45" t="str">
+        <f>K44</f>
+        <v>Vigil Mechanism</v>
+      </c>
+      <c r="D40" s="6" t="str">
+        <f>$L$49</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="6" t="str">
+        <f>$M$49</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="G40" s="54"/>
+      <c r="K40" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="L40" s="46" t="str">
+        <f>IF($D$21&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M40" s="47"/>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="C41" s="45" t="str">
+        <f>K51</f>
+        <v>Internal Financial Controls</v>
+      </c>
+      <c r="D41" s="6" t="str">
+        <f>$L$56</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="54"/>
+      <c r="K41" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="L41" s="46" t="str">
+        <f>D38</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M41" s="47"/>
+    </row>
+    <row r="42" spans="1:13" ht="16.149999999999999" thickBot="1">
+      <c r="C42" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="D42" s="6" t="str">
+        <f>$L$75</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="6" t="str">
+        <f>$M$75</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="G42" s="54"/>
+      <c r="K42" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="L42" s="57" t="str">
+        <f>IF(OR($L$38=I$6,$L$39=$I$6,$L$40=$I$6,$L$41=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M42" s="58"/>
+    </row>
+    <row r="43" spans="1:13" ht="16.149999999999999" thickBot="1">
+      <c r="C43" s="45" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="6" t="str">
+        <f>$L$83</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="6" t="str">
+        <f>$M$83</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="G43" s="54"/>
+      <c r="K43" s="79"/>
+      <c r="L43" s="80"/>
+      <c r="M43" s="81"/>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="C44" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="6" t="str">
+        <f>IF($D$8&gt;100000000,"To appoint CS","Need not appoint CS")</f>
+        <v>Need not appoint CS</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="6" t="str">
+        <f>IF($F$8&gt;100000000,"To appoint CS","Need not appoint CS")</f>
+        <v>Need not appoint CS</v>
+      </c>
+      <c r="G44" s="54"/>
+      <c r="K44" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="L44" s="43"/>
+      <c r="M44" s="41"/>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="C45" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="6" t="str">
+        <f>$L$97</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="54"/>
+      <c r="K45" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M45" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="C46" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="D46" s="6" t="str">
+        <f>IF($D$11&gt;0,"Check for Sec 185 Compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="47"/>
+      <c r="K46" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M46" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="62.45">
+      <c r="C47" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K47" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="L47" s="46" t="str">
+        <f>IF($D$10&gt;500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M47" s="85" t="str">
+        <f>IF($F$10&gt;500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="62.45">
+      <c r="C48" s="45" t="s">
+        <v>176</v>
+      </c>
+      <c r="D48" s="6" t="str">
+        <f>IF($D$17&gt;0,"Whether the Company filed CHG form","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F48" s="6" t="str">
+        <f>IF($F$17&gt;0,"Whether the Company filed CHG form","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="K48" s="45"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="47"/>
+    </row>
+    <row r="49" spans="3:13" ht="77.25">
+      <c r="C49" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="47"/>
+      <c r="K49" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="L49" s="57" t="str">
+        <f>IF(OR($L$45=$I$6,$L$46=$I$6,$L$47=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M49" s="87" t="str">
+        <f>IF(OR($M$45=$I$6,$M$46=$I$6,$M$47=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="50" spans="3:13" ht="39.75" customHeight="1" thickBot="1">
+      <c r="C50" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="6" t="str">
+        <f>IF(($D$24+$D$25+$D$26+$D$27+$D$28)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="47"/>
+      <c r="K50" s="79"/>
+      <c r="L50" s="80"/>
+      <c r="M50" s="81"/>
+    </row>
+    <row r="51" spans="3:13">
+      <c r="C51" s="45" t="s">
+        <v>180</v>
+      </c>
+      <c r="D51" s="6" t="str">
+        <f>IF(($D$24+$D$25+$D$26+$D$27+$D$28)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="47"/>
+      <c r="K51" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="L51" s="43"/>
+      <c r="M51" s="41"/>
+    </row>
+    <row r="52" spans="3:13">
+      <c r="C52" s="45" t="str">
+        <f>K23</f>
+        <v>Corporate Social Responsibility</v>
+      </c>
+      <c r="D52" s="6" t="str">
+        <f>$L$29</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="6" t="str">
+        <f>$M$29</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="G52" s="47"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="47"/>
+    </row>
+    <row r="53" spans="3:13">
+      <c r="C53" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53" s="6" t="str">
+        <f>IF((($D$23+$F$23+$H$22)*2%)&gt;5000000,"Check CSR Committee compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6" t="str">
+        <f>IF((($F$23+$H$22+$I$22)*2%)&gt;5000000,"Check CSR Committee compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="G53" s="47"/>
+      <c r="K53" s="99" t="s">
+        <v>183</v>
+      </c>
+      <c r="L53" s="46" t="str">
+        <f>L9</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M53" s="47"/>
+    </row>
+    <row r="54" spans="3:13" ht="31.15">
+      <c r="C54" s="45" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" s="6" t="str">
+        <f>IF($D$15&gt;0,"Applicable, Is deposit declaration obtained","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="100"/>
+      <c r="G54" s="47"/>
+      <c r="K54" s="99" t="s">
+        <v>185</v>
+      </c>
+      <c r="L54" s="46" t="str">
+        <f>IF((AND($D$21&gt;50000000,$D$10&gt;250000000)), $I$6, $I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M54" s="47"/>
+    </row>
+    <row r="55" spans="3:13" ht="31.15">
+      <c r="C55" s="101" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" s="6" t="str">
+        <f>IF(($D$10+$D$18)&gt;0,"Applicable, Is  Form DPT 3  filed","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K55" s="84"/>
+      <c r="L55" s="46"/>
+      <c r="M55" s="47"/>
+    </row>
+    <row r="56" spans="3:13" ht="31.9" thickBot="1">
+      <c r="C56" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="D56" s="6" t="str">
+        <f>IF($D$19&gt;0,"Applicable, Is Form MSME filed","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K56" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="L56" s="57" t="str">
+        <f>IF(AND($L$53=$I$6,$L$54=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M56" s="58"/>
+    </row>
+    <row r="57" spans="3:13" ht="31.15">
+      <c r="C57" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="D57" s="6" t="str">
+        <f>IF($D$30&gt;0,"Ben Compliance to be checked","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K57" s="59"/>
+      <c r="L57" s="60"/>
+      <c r="M57" s="61"/>
+    </row>
+    <row r="58" spans="3:13">
+      <c r="C58" s="45" t="str">
+        <f>K58</f>
+        <v>MGT 8 Applicability</v>
+      </c>
+      <c r="D58" s="6" t="str">
+        <f>$L64</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="47"/>
+      <c r="K58" s="102" t="s">
+        <v>190</v>
+      </c>
+      <c r="L58" s="5"/>
+      <c r="M58" s="47"/>
+    </row>
+    <row r="59" spans="3:13" ht="16.149999999999999" thickBot="1">
+      <c r="C59" s="103" t="str">
+        <f>K66</f>
+        <v>Certification of MGT 7</v>
+      </c>
+      <c r="D59" s="104" t="str">
+        <f>$L$69</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="E59" s="105"/>
+      <c r="F59" s="104"/>
+      <c r="G59" s="58"/>
+      <c r="K59" s="98"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="47"/>
+    </row>
+    <row r="60" spans="3:13">
+      <c r="K60" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="L60" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M60" s="47"/>
+    </row>
+    <row r="61" spans="3:13">
+      <c r="C61" s="133"/>
+      <c r="K61" s="101" t="s">
+        <v>192</v>
+      </c>
+      <c r="L61" s="46" t="str">
+        <f>IF($D$8&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M61" s="47"/>
+    </row>
+    <row r="62" spans="3:13">
+      <c r="C62" s="133"/>
+      <c r="K62" s="101" t="s">
+        <v>193</v>
+      </c>
+      <c r="L62" s="46" t="str">
+        <f>IF($D$21&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M62" s="47"/>
+    </row>
+    <row r="63" spans="3:13">
+      <c r="E63"/>
+      <c r="K63" s="101"/>
+      <c r="L63" s="46"/>
+      <c r="M63" s="47"/>
+    </row>
+    <row r="64" spans="3:13">
+      <c r="K64" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="L64" s="50" t="str">
+        <f>IF(OR($L$60=$I$6,$L$61=$I$6,$L$62=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M64" s="47"/>
+    </row>
+    <row r="65" spans="11:13">
+      <c r="K65" s="101"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="47"/>
+    </row>
+    <row r="66" spans="11:13">
+      <c r="K66" s="106" t="s">
+        <v>194</v>
+      </c>
+      <c r="L66" s="5"/>
+      <c r="M66" s="47"/>
+    </row>
+    <row r="67" spans="11:13" ht="31.15">
+      <c r="K67" s="101" t="s">
+        <v>195</v>
+      </c>
+      <c r="L67" s="46" t="str">
+        <f>L9</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M67" s="47"/>
+    </row>
+    <row r="68" spans="11:13">
+      <c r="K68" s="101"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="47"/>
+    </row>
+    <row r="69" spans="11:13">
+      <c r="K69" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="L69" s="50" t="str">
+        <f>IF(OR(L67=$I$6,),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M69" s="47"/>
+    </row>
+    <row r="70" spans="11:13">
+      <c r="K70" s="45"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="47"/>
+    </row>
+    <row r="71" spans="11:13">
+      <c r="K71" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="L71" s="5"/>
+      <c r="M71" s="47"/>
+    </row>
+    <row r="72" spans="11:13">
+      <c r="K72" s="107" t="s">
+        <v>196</v>
+      </c>
+      <c r="L72" s="46" t="str">
+        <f>IF($D$21&gt;=2000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M72" s="85" t="str">
+        <f>IF($F$21&gt;=2000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="73" spans="11:13">
+      <c r="K73" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="L73" s="46" t="str">
+        <f>IF($D$10&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M73" s="85" t="str">
+        <f>IF($F$10&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="74" spans="11:13">
+      <c r="K74" s="48"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="47"/>
+    </row>
+    <row r="75" spans="11:13">
+      <c r="K75" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="L75" s="50" t="str">
+        <f>IF(OR($L$72=$I$6,$L$73=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M75" s="108" t="str">
+        <f>IF(OR(M72=$I$6,M73=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="76" spans="11:13">
+      <c r="K76" s="45"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="47"/>
+    </row>
+    <row r="77" spans="11:13">
+      <c r="K77" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="L77" s="5"/>
+      <c r="M77" s="47"/>
+    </row>
+    <row r="78" spans="11:13">
+      <c r="K78" s="109"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="47"/>
+    </row>
+    <row r="79" spans="11:13">
+      <c r="K79" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="L79" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53">
-        <f>C8/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="52"/>
-      <c r="F8" s="54">
-        <f t="shared" ref="F8:F16" si="0">E8/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="55" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="45"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="47"/>
-    </row>
-    <row r="9" spans="1:24" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="52"/>
-      <c r="D9" s="53">
-        <f t="shared" ref="D9:D30" si="1">C9/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="52"/>
-      <c r="F9" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="55" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" s="57" t="str">
-        <f>IF(OR($K$6=$H$6,$K$7=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L9" s="58"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E10" s="52"/>
-      <c r="F10" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="J10" s="59"/>
-      <c r="K10" s="60"/>
-      <c r="L10" s="61"/>
-    </row>
-    <row r="11" spans="1:24" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E11" s="52"/>
-      <c r="F11" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="62"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="64"/>
-      <c r="T11" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="51" t="s">
+      <c r="M79" s="47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="11:13" ht="31.15">
+      <c r="K80" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M80" s="47" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="81" spans="11:13">
+      <c r="K81" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="L81" s="46" t="str">
+        <f>IF($D$10&gt;1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M81" s="85" t="str">
+        <f>IF($F$10&gt;1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="82" spans="11:13">
+      <c r="K82" s="45"/>
+      <c r="L82" s="46"/>
+      <c r="M82" s="85"/>
+    </row>
+    <row r="83" spans="11:13">
+      <c r="K83" s="99" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="H12" s="65">
-        <f>$E$20*0.6</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="K12" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="L12" s="41"/>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E13" s="52"/>
-      <c r="F13" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" s="65">
-        <f>$E$9</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L13" s="47"/>
-      <c r="S13" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="B14" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="65">
-        <f>MAX($H$12,$H$13)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="45" t="s">
-        <v>92</v>
-      </c>
-      <c r="K14" s="46" t="str">
-        <f>K9</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L14" s="47"/>
-      <c r="S14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="U14" s="68" t="s">
-        <v>93</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="66" t="s">
+      <c r="L83" s="50" t="str">
+        <f>IF(OR(L79=$I$6,L80=$I$6,L81=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M83" s="108" t="str">
+        <f>IF(OR(M79=$I$6,M80=$I$6,M81=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="84" spans="11:13">
+      <c r="K84" s="45"/>
+      <c r="L84" s="5"/>
+      <c r="M84" s="47"/>
+    </row>
+    <row r="85" spans="11:13">
+      <c r="K85" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="L85" s="5"/>
+      <c r="M85" s="47"/>
+    </row>
+    <row r="86" spans="11:13">
+      <c r="K86" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="L86" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E15" s="52"/>
-      <c r="F15" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="J15" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="K15" s="46" t="str">
-        <f>IF((AND($C$8&lt;40000000,$C$21&lt;400000000)), $H$7, $H$6)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L15" s="47"/>
-      <c r="V15" s="69" t="s">
-        <v>98</v>
-      </c>
-      <c r="W15" s="70" t="s">
-        <v>99</v>
-      </c>
-      <c r="X15" s="71" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E16" s="52"/>
-      <c r="F16" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="J16" s="72" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="46" t="str">
-        <f>IF(($C$8+$C$9)&gt;10000000,$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L16" s="47"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="52"/>
-      <c r="D17" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E17" s="73"/>
-      <c r="F17" s="54">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="J17" s="72" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17" s="46" t="str">
-        <f>IF($C$10&gt;10000000, $H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L17" s="47"/>
-    </row>
-    <row r="18" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="52"/>
-      <c r="D18" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E18" s="73"/>
-      <c r="F18" s="54">
-        <f t="shared" ref="F18:F29" si="2">E18/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="J18" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="K18" s="46" t="str">
-        <f>IF($C$22&gt;100000000,$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L18" s="47"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="74"/>
-      <c r="D19" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E19" s="73"/>
-      <c r="F19" s="54">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="47"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B20" s="75" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="76">
-        <f>+C8+C9</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="76">
-        <f>+E8+E9</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="54">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="46"/>
-      <c r="L20" s="47"/>
-    </row>
-    <row r="21" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="52"/>
-      <c r="D21" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E21" s="52"/>
-      <c r="F21" s="54">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="J21" s="77" t="s">
-        <v>75</v>
-      </c>
-      <c r="K21" s="57" t="str">
-        <f>IF(OR(K13=$H$6,K14=$H$6,K16=$H$6,K17=$H$6,K18=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L21" s="58"/>
-    </row>
-    <row r="22" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="52"/>
-      <c r="D22" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E22" s="52"/>
-      <c r="F22" s="54">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="J22" s="79"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="81"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>115</v>
-      </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E23" s="52"/>
-      <c r="F23" s="54">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="82" t="s">
-        <v>116</v>
-      </c>
-      <c r="K23" s="43"/>
-      <c r="L23" s="41"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="83"/>
-      <c r="D24" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="84"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="47"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="85" t="s">
-        <v>119</v>
-      </c>
-      <c r="K25" s="46" t="str">
-        <f>IF($C$20&gt;=5000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L25" s="86" t="str">
-        <f>IF($E$20&gt;=5000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="85" t="s">
-        <v>121</v>
-      </c>
-      <c r="K26" s="46" t="str">
-        <f>IF($C$21&gt;=10000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L26" s="86" t="str">
-        <f>IF($E$21&gt;=10000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C27" s="73"/>
-      <c r="D27" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="85" t="s">
-        <v>122</v>
-      </c>
-      <c r="K27" s="46" t="str">
-        <f>IF($C$23&gt;=50000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L27" s="86" t="str">
-        <f>IF($E$23&gt;=50000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="45" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="73"/>
-      <c r="D28" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="85"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="86"/>
-    </row>
-    <row r="29" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="C29" s="73"/>
-      <c r="D29" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="47">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="K29" s="57" t="str">
-        <f>IF(OR($K$25=$H$6,$K$26=$H$6,$K$27=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L29" s="88" t="str">
-        <f>IF(OR($L$25=$H$6,$L$26=$H$6,$L$27=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="74"/>
-      <c r="D30" s="53">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="54">
-        <f>E30/10000000</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="79"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="81"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" s="45" t="s">
-        <v>127</v>
-      </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="47"/>
-      <c r="J31" s="89" t="s">
-        <v>128</v>
-      </c>
-      <c r="K31" s="43"/>
-      <c r="L31" s="41"/>
-    </row>
-    <row r="32" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="J32" s="85" t="s">
-        <v>131</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L32" s="47"/>
-    </row>
-    <row r="33" spans="2:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C33" s="119" t="s">
-        <v>55</v>
-      </c>
-      <c r="D33" s="119"/>
-      <c r="E33" s="120" t="s">
-        <v>132</v>
-      </c>
-      <c r="F33" s="120"/>
-      <c r="J33" s="85" t="s">
-        <v>133</v>
-      </c>
-      <c r="K33" s="46" t="str">
-        <f>IF($C$8&gt;=500000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L33" s="47"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B34" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="90" t="s">
-        <v>59</v>
-      </c>
-      <c r="F34" s="91" t="s">
-        <v>135</v>
-      </c>
-      <c r="J34" s="85"/>
-      <c r="K34" s="46"/>
-      <c r="L34" s="47"/>
-    </row>
-    <row r="35" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="92" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="93" t="str">
-        <f>IF((OR($K$9=$H$6,$K$9=$H$6)), "No, It is not a Small Company", "Yes, It is a Small Company")</f>
-        <v>Yes, It is a Small Company</v>
-      </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="93"/>
-      <c r="F35" s="95"/>
-      <c r="J35" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="K35" s="57" t="str">
-        <f>IF(OR($K$32=$H$6,$K$33=$H$6,),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L35" s="58"/>
-    </row>
-    <row r="36" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="45" t="str">
-        <f>J12</f>
-        <v>CARO</v>
-      </c>
-      <c r="C36" s="6" t="str">
-        <f>$K$21</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="54"/>
-      <c r="J36" s="79"/>
-      <c r="K36" s="80"/>
-      <c r="L36" s="81"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="str">
-        <f>J31</f>
-        <v>Rotation of Auditors</v>
-      </c>
-      <c r="C37" s="6" t="str">
-        <f>$K$35</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D37" s="5"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="54"/>
-      <c r="J37" s="96" t="s">
-        <v>137</v>
-      </c>
-      <c r="K37" s="97"/>
-      <c r="L37" s="41"/>
-    </row>
-    <row r="38" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="C38" s="98" t="str">
-        <f>IF(OR($C$32=$H$6,$C$20&gt;=2500000000,),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="54"/>
-      <c r="J38" s="99" t="s">
-        <v>139</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="L38" s="47"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B39" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="C39" s="6" t="str">
-        <f>$K$42</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D39" s="5"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="54"/>
-      <c r="J39" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="K39" s="46" t="str">
-        <f>IF($C$8&gt;=50000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L39" s="47"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B40" s="45" t="str">
-        <f>J44</f>
-        <v>Vigil Mechanism</v>
-      </c>
-      <c r="C40" s="6" t="str">
-        <f>$K$49</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D40" s="5"/>
-      <c r="E40" s="6" t="str">
-        <f>$L$49</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="F40" s="54"/>
-      <c r="J40" s="99" t="s">
-        <v>142</v>
-      </c>
-      <c r="K40" s="46" t="str">
-        <f>IF($C$21&gt;=1000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L40" s="47"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B41" s="45" t="str">
-        <f>J51</f>
-        <v>Internal Financial Controls</v>
-      </c>
-      <c r="C41" s="6" t="str">
-        <f>$K$56</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="54"/>
-      <c r="J41" s="99" t="s">
-        <v>143</v>
-      </c>
-      <c r="K41" s="46" t="str">
-        <f>C38</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L41" s="47"/>
-    </row>
-    <row r="42" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="C42" s="6" t="str">
-        <f>$K$75</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D42" s="5"/>
-      <c r="E42" s="6" t="str">
-        <f>$L$75</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="F42" s="54"/>
-      <c r="J42" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="K42" s="57" t="str">
-        <f>IF(OR($K$38=H$6,$K$39=$H$6,$K$40=$H$6,$K$41=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L42" s="58"/>
-    </row>
-    <row r="43" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B43" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="C43" s="6" t="str">
-        <f>$K$83</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D43" s="5"/>
-      <c r="E43" s="6" t="str">
-        <f>$L$83</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="F43" s="54"/>
-      <c r="J43" s="79"/>
-      <c r="K43" s="80"/>
-      <c r="L43" s="81"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B44" s="45" t="s">
-        <v>146</v>
-      </c>
-      <c r="C44" s="6" t="str">
-        <f>IF($C$8&gt;100000000,"To appoint CS","Need not appoint CS")</f>
-        <v>Need not appoint CS</v>
-      </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="6" t="str">
-        <f>IF($E$8&gt;100000000,"To appoint CS","Need not appoint CS")</f>
-        <v>Need not appoint CS</v>
-      </c>
-      <c r="F44" s="54"/>
-      <c r="J44" s="39" t="s">
-        <v>147</v>
-      </c>
-      <c r="K44" s="43"/>
-      <c r="L44" s="41"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B45" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="C45" s="6" t="str">
-        <f>$K$97</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D45" s="5"/>
-      <c r="E45" s="6"/>
-      <c r="F45" s="54"/>
-      <c r="J45" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L45" s="47" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B46" s="123" t="s">
-        <v>150</v>
-      </c>
-      <c r="C46" s="6" t="str">
-        <f>IF($C$11&gt;0,"Check for Sec 185 Compliance","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="47"/>
-      <c r="J46" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="K46" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L46" s="47" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="47" spans="2:12" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="B47" s="45" t="s">
-        <v>152</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J47" s="45" t="s">
-        <v>156</v>
-      </c>
-      <c r="K47" s="46" t="str">
-        <f>IF($C$10&gt;500000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L47" s="86" t="str">
-        <f>IF($E$10&gt;500000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="C48" s="6" t="str">
-        <f>IF($C$17&gt;0,"Whether the Company filed CHG form","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="E48" s="6" t="str">
-        <f>IF($E$17&gt;0,"Whether the Company filed CHG form","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J48" s="45"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="47"/>
-    </row>
-    <row r="49" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="45" t="s">
-        <v>158</v>
-      </c>
-      <c r="C49" s="6" t="str">
-        <f>IF($C$31=$H$9,"Applicable, Check AOC 1 is annexed with Board's report","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D49" s="5"/>
-      <c r="E49" s="6"/>
-      <c r="F49" s="47"/>
-      <c r="J49" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="K49" s="57" t="str">
-        <f>IF(OR($K$45=$H$6,$K$46=$H$6,$K$47=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L49" s="88" t="str">
-        <f>IF(OR($L$45=$H$6,$L$46=$H$6,$L$47=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="50" spans="2:12" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C50" s="6" t="str">
-        <f>IF(($C$24+$C$25+$C$26+$C$27+$C$28)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D50" s="5"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="47"/>
-      <c r="J50" s="79"/>
-      <c r="K50" s="80"/>
-      <c r="L50" s="81"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B51" s="123" t="s">
-        <v>160</v>
-      </c>
-      <c r="C51" s="6" t="str">
-        <f>IF(($C$24+$C$25+$C$26+$C$27+$C$28)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="6"/>
-      <c r="F51" s="47"/>
-      <c r="J51" s="39" t="s">
-        <v>161</v>
-      </c>
-      <c r="K51" s="43"/>
-      <c r="L51" s="41"/>
-    </row>
-    <row r="52" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B52" s="45" t="str">
-        <f>J23</f>
-        <v>Corporate Social Responsibility</v>
-      </c>
-      <c r="C52" s="6" t="str">
-        <f>$K$29</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D52" s="5"/>
-      <c r="E52" s="6" t="str">
-        <f>$L$29</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="F52" s="47"/>
-      <c r="J52" s="85"/>
-      <c r="K52" s="5"/>
-      <c r="L52" s="47"/>
-    </row>
-    <row r="53" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B53" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="C53" s="6" t="str">
-        <f>IF((($C$23+$E$23+$G$22)*2%)&gt;5000000,"Check CSR Committee compliance","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D53" s="5"/>
-      <c r="E53" s="6" t="str">
-        <f>IF((($E$23+$G$22+$H$22)*2%)&gt;5000000,"Check CSR Committee compliance","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="F53" s="47"/>
-      <c r="J53" s="100" t="s">
-        <v>163</v>
-      </c>
-      <c r="K53" s="46" t="str">
-        <f>K9</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L53" s="47"/>
-    </row>
-    <row r="54" spans="2:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B54" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="C54" s="6" t="str">
-        <f>IF($C$15&gt;0,"Applicable, Is deposit declaration obtained","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D54" s="5"/>
-      <c r="E54" s="101"/>
-      <c r="F54" s="47"/>
-      <c r="J54" s="100" t="s">
-        <v>165</v>
-      </c>
-      <c r="K54" s="46" t="str">
-        <f>IF((AND($C$21&gt;50000000,$C$10&gt;250000000)), $H$6, $H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L54" s="47"/>
-    </row>
-    <row r="55" spans="2:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B55" s="102" t="s">
-        <v>166</v>
-      </c>
-      <c r="C55" s="6" t="str">
-        <f>IF(($C$10+$C$18)&gt;0,"Applicable, Is  Form DPT 3  filed","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="J55" s="85"/>
-      <c r="K55" s="46"/>
-      <c r="L55" s="47"/>
-    </row>
-    <row r="56" spans="2:12" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B56" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="C56" s="6" t="str">
-        <f>IF($C$19&gt;0,"Applicable, Is Form MSME filed","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="J56" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="K56" s="57" t="str">
-        <f>IF(AND($K$53=$H$6,$K$54=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L56" s="58"/>
-    </row>
-    <row r="57" spans="2:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="B57" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="C57" s="6" t="str">
-        <f>IF($C$30&gt;0,"Ben Compliance to be checked","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="J57" s="59"/>
-      <c r="K57" s="60"/>
-      <c r="L57" s="61"/>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B58" s="45" t="str">
-        <f>J58</f>
-        <v>MGT 8 Applicability</v>
-      </c>
-      <c r="C58" s="6" t="str">
-        <f>$K64</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D58" s="5"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="47"/>
-      <c r="J58" s="103" t="s">
-        <v>170</v>
-      </c>
-      <c r="K58" s="5"/>
-      <c r="L58" s="47"/>
-    </row>
-    <row r="59" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="104" t="str">
-        <f>J66</f>
-        <v>Certification of MGT 7</v>
-      </c>
-      <c r="C59" s="105" t="str">
-        <f>$K$69</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="D59" s="106"/>
-      <c r="E59" s="105"/>
-      <c r="F59" s="58"/>
-      <c r="J59" s="99"/>
-      <c r="K59" s="5"/>
-      <c r="L59" s="47"/>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="J60" s="102" t="s">
-        <v>171</v>
-      </c>
-      <c r="K60" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L60" s="47"/>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B61" s="70"/>
-      <c r="J61" s="102" t="s">
-        <v>172</v>
-      </c>
-      <c r="K61" s="46" t="str">
-        <f>IF($C$8&gt;=100000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L61" s="47"/>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B62" s="70"/>
-      <c r="J62" s="102" t="s">
-        <v>173</v>
-      </c>
-      <c r="K62" s="46" t="str">
-        <f>IF($C$21&gt;=500000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L62" s="47"/>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="D63"/>
-      <c r="J63" s="102"/>
-      <c r="K63" s="46"/>
-      <c r="L63" s="47"/>
-    </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="J64" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K64" s="50" t="str">
-        <f>IF(OR($K$60=$H$6,$K$61=$H$6,$K$62=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L64" s="47"/>
-    </row>
-    <row r="65" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J65" s="102"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="47"/>
-    </row>
-    <row r="66" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J66" s="107" t="s">
-        <v>174</v>
-      </c>
-      <c r="K66" s="5"/>
-      <c r="L66" s="47"/>
-    </row>
-    <row r="67" spans="10:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="J67" s="102" t="s">
-        <v>175</v>
-      </c>
-      <c r="K67" s="46" t="str">
-        <f>K9</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L67" s="47"/>
-    </row>
-    <row r="68" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J68" s="102"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="47"/>
-    </row>
-    <row r="69" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J69" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K69" s="50" t="str">
-        <f>IF(OR(K67=$H$6,),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L69" s="47"/>
-    </row>
-    <row r="70" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J70" s="45"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="47"/>
-    </row>
-    <row r="71" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J71" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="K71" s="5"/>
-      <c r="L71" s="47"/>
-    </row>
-    <row r="72" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J72" s="108" t="s">
-        <v>176</v>
-      </c>
-      <c r="K72" s="46" t="str">
-        <f>IF($C$21&gt;=2000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L72" s="86" t="str">
-        <f>IF($E$21&gt;=2000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="73" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J73" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="K73" s="46" t="str">
-        <f>IF($C$10&gt;=1000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L73" s="86" t="str">
-        <f>IF($E$10&gt;=1000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="74" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J74" s="48"/>
-      <c r="K74" s="5"/>
-      <c r="L74" s="47"/>
-    </row>
-    <row r="75" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J75" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K75" s="50" t="str">
-        <f>IF(OR($K$72=$H$6,$K$73=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L75" s="109" t="str">
-        <f>IF(OR(L72=$H$6,L73=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="76" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J76" s="45"/>
-      <c r="K76" s="5"/>
-      <c r="L76" s="47"/>
-    </row>
-    <row r="77" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J77" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="K77" s="5"/>
-      <c r="L77" s="47"/>
-    </row>
-    <row r="78" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J78" s="110"/>
-      <c r="K78" s="5"/>
-      <c r="L78" s="47"/>
-    </row>
-    <row r="79" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J79" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="K79" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L79" s="47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="80" spans="10:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="J80" s="51" t="s">
-        <v>178</v>
-      </c>
-      <c r="K80" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L80" s="47" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="81" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J81" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="K81" s="46" t="str">
-        <f>IF($C$10&gt;1000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L81" s="86" t="str">
-        <f>IF($E$10&gt;1000000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="82" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J82" s="45"/>
-      <c r="K82" s="46"/>
-      <c r="L82" s="86"/>
-    </row>
-    <row r="83" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J83" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K83" s="50" t="str">
-        <f>IF(OR(K79=$H$6,K80=$H$6,K81=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L83" s="109" t="str">
-        <f>IF(OR(L79=$H$6,L80=$H$6,L81=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="84" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J84" s="45"/>
-      <c r="K84" s="5"/>
-      <c r="L84" s="47"/>
-    </row>
-    <row r="85" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J85" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="K85" s="5"/>
-      <c r="L85" s="47"/>
-    </row>
-    <row r="86" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J86" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L86" s="47" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J87" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="L87" s="47" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J88" s="45" t="s">
-        <v>183</v>
-      </c>
-      <c r="K88" s="46" t="str">
-        <f>IF($C$8&gt;=100000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L88" s="86" t="str">
-        <f>IF($E$8&gt;=100000000,"Applicable","Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="89" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J89" s="45"/>
-      <c r="K89" s="46"/>
-      <c r="L89" s="86"/>
-    </row>
-    <row r="90" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J90" s="100" t="s">
-        <v>75</v>
-      </c>
-      <c r="K90" s="50" t="str">
-        <f>IF(OR(K86=$H$6,K87=$H$6,K88=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L90" s="109" t="str">
-        <f>IF(OR(L86=$H$6,L87=$H$6,L88=$H$6),$H$6,$H$7)</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="91" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J91" s="45"/>
-      <c r="K91" s="5"/>
-      <c r="L91" s="47"/>
-    </row>
-    <row r="92" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J92" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="K92" s="5"/>
-      <c r="L92" s="47"/>
-    </row>
-    <row r="93" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J93" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="K93" s="5" t="str">
-        <f>IF(($C$12+$C$13+$C$14)&gt;$H$14,"Check for Shareholders approval","Check for Boards Approval")</f>
+      <c r="M86" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="11:13">
+      <c r="K87" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="M87" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="11:13">
+      <c r="K88" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="L88" s="46" t="str">
+        <f>IF($D$8&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M88" s="85" t="str">
+        <f>IF($F$8&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="89" spans="11:13">
+      <c r="K89" s="45"/>
+      <c r="L89" s="46"/>
+      <c r="M89" s="85"/>
+    </row>
+    <row r="90" spans="11:13">
+      <c r="K90" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="L90" s="50" t="str">
+        <f>IF(OR(L86=$I$6,L87=$I$6,L88=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M90" s="108" t="str">
+        <f>IF(OR(M86=$I$6,M87=$I$6,M88=$I$6),$I$6,$I$7)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="91" spans="11:13">
+      <c r="K91" s="45"/>
+      <c r="L91" s="5"/>
+      <c r="M91" s="47"/>
+    </row>
+    <row r="92" spans="11:13">
+      <c r="K92" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="L92" s="5"/>
+      <c r="M92" s="47"/>
+    </row>
+    <row r="93" spans="11:13">
+      <c r="K93" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="L93" s="5" t="str">
+        <f>IF(($D$12+$D$13+$D$14)&gt;$I$14,"Check for Shareholders approval","Check for Boards Approval")</f>
         <v>Check for Boards Approval</v>
       </c>
-      <c r="L93" s="47" t="str">
-        <f>IF(($E$12+$E$13+$E$14)&gt;$H$14,"Check for Shareholders approval","Check for Boards Approval")</f>
+      <c r="M93" s="47" t="str">
+        <f>IF(($F$12+$F$13+$F$14)&gt;$I$14,"Check for Shareholders approval","Check for Boards Approval")</f>
         <v>Check for Boards Approval</v>
       </c>
     </row>
-    <row r="94" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J94" s="45" t="s">
-        <v>186</v>
-      </c>
-      <c r="K94" s="5" t="str">
-        <f>IF(($C$12+$C$13+$C$14)&gt;0,$K$93,"Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L94" s="47" t="str">
-        <f>IF(($E$12+$E$13+$E$14)&gt;0,$L$93,"Not Applicable")</f>
-        <v>Not Applicable</v>
-      </c>
-    </row>
-    <row r="95" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J95" s="45"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="47"/>
-    </row>
-    <row r="96" spans="10:12" x14ac:dyDescent="0.3">
-      <c r="J96" s="45"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="47"/>
-    </row>
-    <row r="97" spans="10:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J97" s="87" t="s">
-        <v>75</v>
-      </c>
-      <c r="K97" s="57" t="str">
-        <f>IF(OR(K93=$H$7,K94=$H$7),$H$7,$K$93)</f>
-        <v>Not Applicable</v>
-      </c>
-      <c r="L97" s="88" t="str">
-        <f>IF(OR(L93=$H$7,L94=$H$7),$H$7,$L$93)</f>
+    <row r="94" spans="11:13">
+      <c r="K94" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="L94" s="5" t="str">
+        <f>IF(($D$12+$D$13+$D$14)&gt;0,$L$93,"Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M94" s="47" t="str">
+        <f>IF(($F$12+$F$13+$F$14)&gt;0,$M$93,"Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="95" spans="11:13">
+      <c r="K95" s="45"/>
+      <c r="L95" s="5"/>
+      <c r="M95" s="47"/>
+    </row>
+    <row r="96" spans="11:13">
+      <c r="K96" s="45"/>
+      <c r="L96" s="5"/>
+      <c r="M96" s="47"/>
+    </row>
+    <row r="97" spans="11:13" ht="16.149999999999999" thickBot="1">
+      <c r="K97" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="L97" s="57" t="str">
+        <f>IF(OR(L93=$I$7,L94=$I$7),$I$7,$L$93)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="M97" s="87" t="str">
+        <f>IF(OR(M93=$I$7,M94=$I$7),$I$7,$M$93)</f>
         <v>Not Applicable</v>
       </c>
     </row>
   </sheetData>
   <dataConsolidate/>
-  <mergeCells count="6">
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
+  <mergeCells count="5">
+    <mergeCell ref="K1:M1"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
   </mergeCells>
-  <conditionalFormatting sqref="C35">
-    <cfRule type="containsText" dxfId="14" priority="11" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",C35)))</formula>
+  <conditionalFormatting sqref="D35">
+    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",D35)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E35">
-    <cfRule type="containsText" dxfId="13" priority="8" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",E35)))</formula>
+  <conditionalFormatting sqref="F35">
+    <cfRule type="containsText" dxfId="29" priority="8" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",F35)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="containsText" dxfId="12" priority="7" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K6)))</formula>
+  <conditionalFormatting sqref="L6">
+    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L6)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K20">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K13)))</formula>
+  <conditionalFormatting sqref="L13:L20">
+    <cfRule type="containsText" dxfId="27" priority="1" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L13)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K33:K34">
-    <cfRule type="containsText" dxfId="10" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K33)))</formula>
+  <conditionalFormatting sqref="L33:L34">
+    <cfRule type="containsText" dxfId="26" priority="14" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L33)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K39:K41">
-    <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K39)))</formula>
+  <conditionalFormatting sqref="L39:L41">
+    <cfRule type="containsText" dxfId="25" priority="13" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L39)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K53:K55">
-    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K53)))</formula>
+  <conditionalFormatting sqref="L53:L55">
+    <cfRule type="containsText" dxfId="24" priority="10" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L53)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K61:K63">
-    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K61)))</formula>
+  <conditionalFormatting sqref="L61:L63">
+    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L61)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K67">
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K67)))</formula>
+  <conditionalFormatting sqref="L67">
+    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L67)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K25:L28">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K25)))</formula>
+  <conditionalFormatting sqref="L25:M28">
+    <cfRule type="containsText" dxfId="21" priority="6" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L25)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K47:L47">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K47)))</formula>
+  <conditionalFormatting sqref="L47:M47">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L47)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K72:L73">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K72)))</formula>
+  <conditionalFormatting sqref="L72:M73">
+    <cfRule type="containsText" dxfId="19" priority="4" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L72)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K81:L82">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K81)))</formula>
+  <conditionalFormatting sqref="L81:M82">
+    <cfRule type="containsText" dxfId="18" priority="3" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L81)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K88:L89">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",K88)))</formula>
+  <conditionalFormatting sqref="L88:M89">
+    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L88)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32" xr:uid="{61511389-8940-41BC-9FD7-27A321295AEA}">
-      <formula1>$H$6:$H$7</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D32" xr:uid="{61511389-8940-41BC-9FD7-27A321295AEA}">
+      <formula1>$I$6:$I$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C31" xr:uid="{33DCB57B-AB8E-4C83-B2AD-B1EE988C48F5}">
-      <formula1>$H$8:$H$10</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D31" xr:uid="{33DCB57B-AB8E-4C83-B2AD-B1EE988C48F5}">
+      <formula1>$I$8:$I$10</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="K25" r:id="rId1" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{943842DE-F9ED-467D-B9FC-FA9E0065C658}"/>
-    <hyperlink ref="K26" r:id="rId2" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{BD5F2BA7-CF90-4C9A-929C-5878F637D18C}"/>
-    <hyperlink ref="K27" r:id="rId3" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{3E78F8B3-56FB-4FE0-86C8-0EB1ACFCAA9A}"/>
-    <hyperlink ref="K47" r:id="rId4" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D8B9ABF2-DC66-4584-9986-FE05E71AB956}"/>
-    <hyperlink ref="K62" r:id="rId5" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{13E64E7E-D0E7-4564-B214-2970740119AC}"/>
-    <hyperlink ref="K61" r:id="rId6" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{11D12BA7-C63C-4C89-BD48-F248BE9BA2DD}"/>
-    <hyperlink ref="C35" r:id="rId7" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{890016B1-8AB9-43A3-80B4-0FB3CA756EFE}"/>
-    <hyperlink ref="K18" r:id="rId8" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{60B5CE62-9C6C-4B6A-A4FB-09A69B024C08}"/>
-    <hyperlink ref="K17" r:id="rId9" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{BA2BFDDA-01F4-45E0-B664-694C6B83D352}"/>
-    <hyperlink ref="K16" r:id="rId10" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{0BF65D57-8666-4848-B510-D159766463BF}"/>
-    <hyperlink ref="K14" r:id="rId11" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D095B7A3-4EC3-4BF6-897C-FC0201BEA10C}"/>
-    <hyperlink ref="K53" r:id="rId12" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{7166EC0F-3469-4B7C-9813-9ACA14DEE46B}"/>
-    <hyperlink ref="K54" r:id="rId13" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{B06581EB-CC89-4B90-B012-2822000D755D}"/>
-    <hyperlink ref="K67" r:id="rId14" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{5D7C692B-D060-4CA5-BB6C-4EE30A425FB5}"/>
-    <hyperlink ref="K72" r:id="rId15" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F6DC73B9-4260-4E0A-B94A-BAFB09BA2914}"/>
-    <hyperlink ref="K73" r:id="rId16" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{75D24E4B-6C74-4F73-AB82-5C807B03740A}"/>
-    <hyperlink ref="K81" r:id="rId17" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A2506AAA-C748-46C7-925D-A4832E153B56}"/>
-    <hyperlink ref="K88" r:id="rId18" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6F3029A7-0A91-4AE4-844C-7EA18E8E4EC2}"/>
-    <hyperlink ref="C44" r:id="rId19" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{533FA124-B5BC-4C95-AD23-B6FA3C36ECE0}"/>
-    <hyperlink ref="K40" r:id="rId20" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{143C46A4-030C-4108-A467-D79E6CB1A7AD}"/>
-    <hyperlink ref="K39" r:id="rId21" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{56510D09-06E9-4150-9C86-E98C316B76CE}"/>
-    <hyperlink ref="K33" r:id="rId22" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F1005A47-DB38-4266-8599-28C7EF0E3A2A}"/>
-    <hyperlink ref="C55" r:id="rId23" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{57C99A49-53FF-494F-9F1A-DE540C27A996}"/>
-    <hyperlink ref="K6" r:id="rId24" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{45071016-A3D3-4362-939B-CCFFF6FCD38B}"/>
-    <hyperlink ref="L25" r:id="rId25" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6B50F12E-39C1-41B5-9F91-5288FEC5E826}"/>
-    <hyperlink ref="L26" r:id="rId26" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A0DC164C-B81F-4003-85F2-DCAF6131ACCF}"/>
-    <hyperlink ref="L27" r:id="rId27" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6E7943C0-AB90-4E1A-95EB-1636AD223C00}"/>
-    <hyperlink ref="L47" r:id="rId28" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{742B0C73-63B9-4F2D-BA98-6E2231BEDDDD}"/>
-    <hyperlink ref="L72" r:id="rId29" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F5AE6230-9767-4191-84B7-EC16B5AB2439}"/>
-    <hyperlink ref="L73" r:id="rId30" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{CBD87B4A-E84A-4B23-B956-EB17FB4A4665}"/>
-    <hyperlink ref="L81" r:id="rId31" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D039354A-ADFA-42DA-9DD0-0D68B5086EAF}"/>
-    <hyperlink ref="L88" r:id="rId32" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{7CFFEE0F-71ED-4143-81DC-00A298ED17CA}"/>
-    <hyperlink ref="E44" r:id="rId33" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{96629993-962A-4481-9899-69F74F6C4675}"/>
-    <hyperlink ref="K15" r:id="rId34" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{CE2A1297-A5A7-4136-B933-B47917A822A1}"/>
-    <hyperlink ref="C48" r:id="rId35" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{E9157EFE-CC7A-4112-AC23-9C3F292A9D98}"/>
-    <hyperlink ref="E48" r:id="rId36" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{380B050C-5579-46FC-8EB4-28C0B006C2D3}"/>
+    <hyperlink ref="L25" r:id="rId1" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{943842DE-F9ED-467D-B9FC-FA9E0065C658}"/>
+    <hyperlink ref="L26" r:id="rId2" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{BD5F2BA7-CF90-4C9A-929C-5878F637D18C}"/>
+    <hyperlink ref="L27" r:id="rId3" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{3E78F8B3-56FB-4FE0-86C8-0EB1ACFCAA9A}"/>
+    <hyperlink ref="L47" r:id="rId4" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D8B9ABF2-DC66-4584-9986-FE05E71AB956}"/>
+    <hyperlink ref="L62" r:id="rId5" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{13E64E7E-D0E7-4564-B214-2970740119AC}"/>
+    <hyperlink ref="L61" r:id="rId6" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{11D12BA7-C63C-4C89-BD48-F248BE9BA2DD}"/>
+    <hyperlink ref="D35" r:id="rId7" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{890016B1-8AB9-43A3-80B4-0FB3CA756EFE}"/>
+    <hyperlink ref="L18" r:id="rId8" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{60B5CE62-9C6C-4B6A-A4FB-09A69B024C08}"/>
+    <hyperlink ref="L17" r:id="rId9" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{BA2BFDDA-01F4-45E0-B664-694C6B83D352}"/>
+    <hyperlink ref="L16" r:id="rId10" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{0BF65D57-8666-4848-B510-D159766463BF}"/>
+    <hyperlink ref="L14" r:id="rId11" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D095B7A3-4EC3-4BF6-897C-FC0201BEA10C}"/>
+    <hyperlink ref="L53" r:id="rId12" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{7166EC0F-3469-4B7C-9813-9ACA14DEE46B}"/>
+    <hyperlink ref="L54" r:id="rId13" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{B06581EB-CC89-4B90-B012-2822000D755D}"/>
+    <hyperlink ref="L67" r:id="rId14" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{5D7C692B-D060-4CA5-BB6C-4EE30A425FB5}"/>
+    <hyperlink ref="L72" r:id="rId15" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F6DC73B9-4260-4E0A-B94A-BAFB09BA2914}"/>
+    <hyperlink ref="L73" r:id="rId16" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{75D24E4B-6C74-4F73-AB82-5C807B03740A}"/>
+    <hyperlink ref="L81" r:id="rId17" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A2506AAA-C748-46C7-925D-A4832E153B56}"/>
+    <hyperlink ref="L88" r:id="rId18" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6F3029A7-0A91-4AE4-844C-7EA18E8E4EC2}"/>
+    <hyperlink ref="D44" r:id="rId19" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{533FA124-B5BC-4C95-AD23-B6FA3C36ECE0}"/>
+    <hyperlink ref="L40" r:id="rId20" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{143C46A4-030C-4108-A467-D79E6CB1A7AD}"/>
+    <hyperlink ref="L39" r:id="rId21" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{56510D09-06E9-4150-9C86-E98C316B76CE}"/>
+    <hyperlink ref="L33" r:id="rId22" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F1005A47-DB38-4266-8599-28C7EF0E3A2A}"/>
+    <hyperlink ref="D55" r:id="rId23" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{57C99A49-53FF-494F-9F1A-DE540C27A996}"/>
+    <hyperlink ref="L6" r:id="rId24" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{45071016-A3D3-4362-939B-CCFFF6FCD38B}"/>
+    <hyperlink ref="M25" r:id="rId25" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6B50F12E-39C1-41B5-9F91-5288FEC5E826}"/>
+    <hyperlink ref="M26" r:id="rId26" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A0DC164C-B81F-4003-85F2-DCAF6131ACCF}"/>
+    <hyperlink ref="M27" r:id="rId27" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6E7943C0-AB90-4E1A-95EB-1636AD223C00}"/>
+    <hyperlink ref="M47" r:id="rId28" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{742B0C73-63B9-4F2D-BA98-6E2231BEDDDD}"/>
+    <hyperlink ref="M72" r:id="rId29" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F5AE6230-9767-4191-84B7-EC16B5AB2439}"/>
+    <hyperlink ref="M73" r:id="rId30" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{CBD87B4A-E84A-4B23-B956-EB17FB4A4665}"/>
+    <hyperlink ref="M81" r:id="rId31" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D039354A-ADFA-42DA-9DD0-0D68B5086EAF}"/>
+    <hyperlink ref="M88" r:id="rId32" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{7CFFEE0F-71ED-4143-81DC-00A298ED17CA}"/>
+    <hyperlink ref="F44" r:id="rId33" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{96629993-962A-4481-9899-69F74F6C4675}"/>
+    <hyperlink ref="L15" r:id="rId34" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{CE2A1297-A5A7-4136-B933-B47917A822A1}"/>
+    <hyperlink ref="D48" r:id="rId35" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{E9157EFE-CC7A-4112-AC23-9C3F292A9D98}"/>
+    <hyperlink ref="F48" r:id="rId36" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{380B050C-5579-46FC-8EB4-28C0B006C2D3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId37"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5E89D1D-3350-4790-B327-21F1F8282FE5}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81BA97EC-21E2-4737-954E-4DC3CF37E1A8}">
+  <dimension ref="A1:P81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="37.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.42578125" style="35" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="33.140625" style="35" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="49.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="24" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="47.28515625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.28515625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:16" ht="16.149999999999999" thickBot="1">
+      <c r="J1" s="36"/>
+      <c r="K1" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" s="38" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="2:16" ht="16.149999999999999" thickBot="1">
+      <c r="B2" s="144" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="J2" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="L2" s="41"/>
+      <c r="N2" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="O2" s="40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16" ht="31.15">
+      <c r="B3" s="42"/>
+      <c r="C3" s="140" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="145"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="45" t="s">
+        <v>209</v>
+      </c>
+      <c r="K3" s="46" t="str">
+        <f>IF((AND($C$5&lt;20000000,$C$17&lt;200000000)), $H$4, $H$3)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L3" s="47"/>
+      <c r="N3" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="O3" s="46" t="str">
+        <f>IF((OR($C$5&gt;=1000000000,$C$17&gt;=3000000000)), $H$3, $H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="P3" s="46" t="str">
+        <f>IF((OR($E$5&gt;=1000000000,$E$17&gt;=3000000000)), $H$3, $H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="16.149999999999999" thickBot="1">
+      <c r="B4" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="114" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="113"/>
+      <c r="H4" s="113" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="K4" s="57" t="str">
+        <f ca="1">IF(OR($K$3=$H$3,$K$4=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L4" s="47"/>
+    </row>
+    <row r="5" spans="2:16" ht="29.45" thickBot="1">
+      <c r="B5" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53">
+        <f>C5/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="52">
+        <f>+C5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="115">
+        <f t="shared" ref="F5:F14" si="0">E5/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="113"/>
+      <c r="H5" s="116" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="45"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="47"/>
+    </row>
+    <row r="6" spans="2:16" ht="16.149999999999999" thickBot="1">
+      <c r="B6" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53">
+        <f t="shared" ref="D6:D22" si="1">C6/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="52"/>
+      <c r="F6" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="113"/>
+      <c r="H6" s="116" t="s">
+        <v>79</v>
+      </c>
+      <c r="J6" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="57" t="str">
+        <f ca="1">IF(OR($K$3=$H$3,$K$4=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L6" s="58"/>
+      <c r="N6" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="O6" s="40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="46.9">
+      <c r="B7" s="51" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="52"/>
+      <c r="D7" s="53">
+        <f>C7/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="52"/>
+      <c r="F7" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G7" s="113"/>
+      <c r="H7" s="116" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="59"/>
+      <c r="K7" s="60"/>
+      <c r="L7" s="61"/>
+      <c r="N7" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="O7" s="46" t="str">
+        <f>IF((OR($C$5&gt;=100000000,$C$17&gt;=1000000000,$C$7&gt;500000000)), $H$3, $H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="P7" s="46" t="str">
+        <f>IF((OR($E$5&gt;=100000000,$E$17&gt;=1000000000,$E$7&gt;500000000)), $H$3, $H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="31.9" thickBot="1">
+      <c r="B8" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="117"/>
+      <c r="F8" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="113"/>
+      <c r="H8" s="113" t="s">
+        <v>214</v>
+      </c>
+      <c r="J8" s="62"/>
+      <c r="K8" s="63"/>
+      <c r="L8" s="64"/>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="52"/>
+      <c r="D9" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="117"/>
+      <c r="F9" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="113"/>
+      <c r="H9" s="113" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="41"/>
+    </row>
+    <row r="10" spans="2:16" ht="16.149999999999999" thickBot="1">
+      <c r="B10" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="52"/>
+      <c r="D10" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="113"/>
+      <c r="H10" s="113"/>
+      <c r="J10" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="47"/>
+    </row>
+    <row r="11" spans="2:16" ht="31.15">
+      <c r="B11" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="J11" s="82" t="s">
+        <v>131</v>
+      </c>
+      <c r="K11" s="43"/>
+      <c r="L11" s="41"/>
+    </row>
+    <row r="12" spans="2:16" ht="31.15">
+      <c r="B12" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" s="52"/>
+      <c r="D12" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="52"/>
+      <c r="F12" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G12" s="113" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="118">
+        <f>$E$16*0.6</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="83"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="47"/>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="B13" s="66" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="52"/>
+      <c r="D13" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="73"/>
+      <c r="F13" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G13" s="113" t="s">
+        <v>94</v>
+      </c>
+      <c r="H13" s="118">
+        <f>$E$6</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="84" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="46" t="str">
+        <f>IF($C$16&gt;=5000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L13" s="85" t="str">
+        <f>IF($E$16&gt;=5000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" ht="31.15">
+      <c r="B14" s="51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="52"/>
+      <c r="D14" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="73"/>
+      <c r="F14" s="115">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G14" s="113" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="118">
+        <f>MAX($H$12,$H$13)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="84" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="46" t="str">
+        <f>IF($C$17&gt;=10000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L14" s="85" t="str">
+        <f>IF($E$17&gt;=10000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16">
+      <c r="B15" s="66" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="74"/>
+      <c r="D15" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="73"/>
+      <c r="F15" s="115">
+        <f>E15/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="113"/>
+      <c r="H15" s="113"/>
+      <c r="J15" s="84" t="s">
+        <v>139</v>
+      </c>
+      <c r="K15" s="46" t="str">
+        <f>IF($C$19&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L15" s="85" t="str">
+        <f>IF($E$19&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16">
+      <c r="B16" s="75" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="76">
+        <f>$C$5+$C$6</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="76"/>
+      <c r="F16" s="115">
+        <f>E16/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="85"/>
+    </row>
+    <row r="17" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="B17" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="52"/>
+      <c r="F17" s="115">
+        <f>E17/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17" s="57" t="str">
+        <f>IF(OR($K$13=$H$3,$K$14=$H$3,$K$15=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L17" s="87" t="str">
+        <f>IF(OR($L$13=$H$3,$L$14=$H$3,$L$15=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="B18" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="52"/>
+      <c r="D18" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="52"/>
+      <c r="F18" s="54">
+        <f>E18/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="79"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="81"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="B19" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="53">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="52"/>
+      <c r="F19" s="54">
+        <f>E19/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="78"/>
+      <c r="H19" s="78"/>
+      <c r="J19" s="88" t="s">
+        <v>147</v>
+      </c>
+      <c r="K19" s="43"/>
+      <c r="L19" s="41"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="B20" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="73"/>
+      <c r="D20" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="47"/>
+      <c r="J20" s="84" t="s">
+        <v>217</v>
+      </c>
+      <c r="K20" s="46" t="str">
+        <f>IF($C$5&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L20" s="46" t="str">
+        <f>IF($E$5&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="B21" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="73"/>
+      <c r="D21" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="47"/>
+      <c r="J21" s="84" t="s">
+        <v>218</v>
+      </c>
+      <c r="K21" s="46" t="str">
+        <f>IF($C$7&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L21" s="46" t="str">
+        <f>IF($E$7&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="B22" s="45" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="73"/>
+      <c r="D22" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="6"/>
+      <c r="F22" s="47"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="47"/>
+    </row>
+    <row r="23" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="B23" s="45" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="73"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="47"/>
+      <c r="J23" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="57" t="str">
+        <f>IF(OR($K$20=$H$3,$K$21=$H$3,),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L23" s="57" t="str">
+        <f>IF(OR($L$20=$H$3,$L$21=$H$3,),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="B24" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" s="73"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="47"/>
+      <c r="J24" s="79"/>
+      <c r="K24" s="80"/>
+      <c r="L24" s="81"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="B25" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="73"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="47"/>
+      <c r="J25" s="95" t="s">
+        <v>156</v>
+      </c>
+      <c r="K25" s="96"/>
+      <c r="L25" s="41"/>
+    </row>
+    <row r="26" spans="1:12" ht="31.15">
+      <c r="B26" s="66" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="74"/>
+      <c r="D26" s="53">
+        <f>C26/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="6"/>
+      <c r="F26" s="54">
+        <f>E26/10000000</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="47"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="B27" s="45" t="s">
+        <v>146</v>
+      </c>
+      <c r="C27" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="47"/>
+      <c r="J27" s="84" t="s">
+        <v>160</v>
+      </c>
+      <c r="K27" s="46" t="str">
+        <f>IF($C$5&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L27" s="46" t="str">
+        <f>IF($E$5&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="B28" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="J28" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="K28" s="46" t="str">
+        <f>IF($C$17&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L28" s="46" t="str">
+        <f>IF($E$17&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="18">
+      <c r="B29" s="5"/>
+      <c r="C29" s="146" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="146"/>
+      <c r="E29" s="147" t="s">
+        <v>63</v>
+      </c>
+      <c r="F29" s="147"/>
+      <c r="J29" s="98" t="s">
+        <v>222</v>
+      </c>
+      <c r="K29" s="50" t="str">
+        <f>IF($C$28=$H$8,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L29" s="50" t="str">
+        <f>IF($E$28=$H$8,"Applicable","Not Applicable")</f>
+        <v>Applicable</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="B30" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="9"/>
+      <c r="J30" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K30" s="57" t="str">
+        <f>IF(OR($K$26=H$3,$K$27=$H$3,$K$28=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L30" s="57" t="str">
+        <f>IF(OR($L$26=I$3,$L$27=$H$3,$L$28=$H$3),$H$3,$H$4)</f>
+        <v>Applicable</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="A31" s="1">
+        <v>1</v>
+      </c>
+      <c r="B31" s="119" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="120" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" s="53"/>
+      <c r="E31" s="121" t="str">
+        <f>C31</f>
+        <v>No it is not a small company</v>
+      </c>
+      <c r="F31" s="53"/>
+      <c r="J31" s="79"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="81"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="1">
+        <v>2</v>
+      </c>
+      <c r="B32" s="5" t="str">
+        <f>J9</f>
+        <v>CARO</v>
+      </c>
+      <c r="C32" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="D32" s="5"/>
+      <c r="E32" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="53"/>
+      <c r="J32" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="K32" s="43"/>
+      <c r="L32" s="41"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="1">
+        <v>3</v>
+      </c>
+      <c r="B33" s="5" t="str">
+        <f>J19</f>
+        <v>Rotation of Auditors</v>
+      </c>
+      <c r="C33" s="122" t="str">
+        <f>$K$23</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="121" t="str">
+        <f>$L$23</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F33" s="53"/>
+      <c r="J33" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L33" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="1">
+        <v>4</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="122" t="str">
+        <f>$K$30</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="121" t="str">
+        <f>L30</f>
+        <v>Applicable</v>
+      </c>
+      <c r="F34" s="53"/>
+      <c r="J34" s="45" t="s">
+        <v>170</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L34" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="1">
+        <v>5</v>
+      </c>
+      <c r="B35" s="5" t="str">
+        <f>J32</f>
+        <v>Vigil Mechanism</v>
+      </c>
+      <c r="C35" s="122" t="str">
+        <f>$K$37</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D35" s="5"/>
+      <c r="E35" s="121" t="str">
+        <f>L37</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F35" s="53"/>
+      <c r="J35" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="K35" s="46" t="str">
+        <f>IF($C$7&gt;500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L35" s="85" t="str">
+        <f>IF($E$7&gt;500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="1">
+        <v>6</v>
+      </c>
+      <c r="B36" s="5" t="str">
+        <f>J39</f>
+        <v>Internal Financial Controls</v>
+      </c>
+      <c r="C36" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="122" t="s">
+        <v>64</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="47"/>
+    </row>
+    <row r="37" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="A37" s="1">
+        <v>7</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="122" t="str">
+        <f>$K$59</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="122" t="str">
+        <f>$L$59</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F37" s="53"/>
+      <c r="J37" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K37" s="57" t="str">
+        <f>IF(OR($K$33=$H$3,$K$34=$H$3,$K$35=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L37" s="87" t="str">
+        <f>IF(OR($L$33=$H$3,$L$34=$H$3,$L$35=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="A38" s="1">
+        <v>8</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" s="122" t="str">
+        <f>$K$67</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="122" t="str">
+        <f>$L$67</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F38" s="53"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="80"/>
+      <c r="L38" s="81"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="1">
+        <v>9</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C39" s="122" t="str">
+        <f>IF($C$5&gt;50000000,"To appoint CS","Need not appoint CS")</f>
+        <v>Need not appoint CS</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="122" t="str">
+        <f>IF($E$5&gt;50000000,"To appoint CS","Need not appoint CS")</f>
+        <v>Need not appoint CS</v>
+      </c>
+      <c r="F39" s="53"/>
+      <c r="J39" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="K39" s="43"/>
+      <c r="L39" s="41"/>
+    </row>
+    <row r="40" spans="1:12" ht="16.149999999999999" thickBot="1">
+      <c r="A40" s="1">
+        <v>10</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C40" s="6" t="str">
+        <f>$K$81</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="6" t="str">
+        <f>$L$81</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F40" s="53"/>
+      <c r="J40" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K40" s="57" t="s">
+        <v>64</v>
+      </c>
+      <c r="L40" s="58"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="1">
+        <v>11</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C41" s="6" t="str">
+        <f>IF($C$8&gt;0,"Check for Sec 185 Compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6" t="str">
+        <f>IF($E$8&gt;0,"Check for Sec 185 Compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F41" s="5"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="61"/>
+    </row>
+    <row r="42" spans="1:12" ht="124.9">
+      <c r="A42" s="1">
+        <v>12</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C42" s="122" t="s">
+        <v>174</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="E42" s="122" t="s">
+        <v>174</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J42" s="102" t="s">
+        <v>190</v>
+      </c>
+      <c r="K42" s="5"/>
+      <c r="L42" s="47"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="1">
+        <v>13</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C43" s="6" t="str">
+        <f>IF($C$27=$H$6,"Applicable, Check AOC 1 is annexed with Board's report","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="6" t="str">
+        <f>IF($E$27=$H$6,"Applicable, Check AOC 1 is annexed with Board's report","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="J43" s="98"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="47"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="1">
+        <v>14</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C44" s="122" t="str">
+        <f>IF(($C$20+$C$21+$C$22+$C$23+$C$24)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="6" t="str">
+        <f>IF(($E$20+$E$21+$E$22+$E$23+$E$24)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="J44" s="101" t="s">
+        <v>191</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L44" s="47"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="1">
+        <v>15</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C45" s="122" t="str">
+        <f>IF(($C$20+$C$21+$C$22+$C$23+$C$24)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="6" t="str">
+        <f>IF(($E$20+$E$21+$E$22+$E$23+$E$24)&gt;0,"Applicable, Fill in Sec 188 Compliance sheet","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F45" s="5"/>
+      <c r="J45" s="101" t="s">
+        <v>192</v>
+      </c>
+      <c r="K45" s="46" t="str">
+        <f>IF($C$5&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L45" s="46" t="str">
+        <f>IF($E$5&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="1">
+        <v>16</v>
+      </c>
+      <c r="B46" s="5" t="str">
+        <f>J11</f>
+        <v>Corporate Social Responsibility</v>
+      </c>
+      <c r="C46" s="6" t="str">
+        <f>$K$17</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="6" t="str">
+        <f>$L$17</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F46" s="5"/>
+      <c r="J46" s="101" t="s">
+        <v>193</v>
+      </c>
+      <c r="K46" s="46" t="str">
+        <f>IF($C$17&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L46" s="46" t="str">
+        <f>IF($E$17&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="1">
+        <v>17</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C47" s="6" t="str">
+        <f>IF((($C$19+$E$19+$G$19)*2%)&gt;5000000,"Check CSR Committee compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D47" s="5"/>
+      <c r="E47" s="6" t="str">
+        <f>IF((($H$19+$E$19+$G$19)*2%)&gt;5000000,"Check CSR Committee compliance","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F47" s="5"/>
+      <c r="J47" s="101"/>
+      <c r="K47" s="46"/>
+      <c r="L47" s="46"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="1">
+        <v>18</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C48" s="6" t="str">
+        <f>IF($C$12&gt;0,"Applicable, Is deposit declaration obtained","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="6" t="str">
+        <f>IF($E$12&gt;0,"Applicable, Is deposit declaration obtained","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F48" s="5"/>
+      <c r="J48" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="K48" s="50" t="str">
+        <f>IF(OR($K$44=$H$3,$K$45=$H$3,$K$46=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L48" s="50" t="str">
+        <f>IF(OR($L$44=$H$3,$L$45=$H$3,$L$46=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="62.45">
+      <c r="A49" s="1">
+        <v>19</v>
+      </c>
+      <c r="B49" s="123" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="122" t="str">
+        <f>IF(($C$7+$C$14)&gt;0,"Applicable, Is  Form DPT 3  filed","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="6" t="str">
+        <f>IF(($E$7+$E$14)&gt;0,"Applicable, Is  Form DPT 3  filed","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="J49" s="101"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="47"/>
+    </row>
+    <row r="50" spans="1:12" ht="62.45">
+      <c r="A50" s="1">
+        <v>20</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C50" s="6" t="str">
+        <f>IF($C$15&gt;0,"Applicable, Is Form MSME filed","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E50" s="6" t="str">
+        <f>IF($E$15&gt;0,"Applicable, Is Form MSME filed","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F50" s="6"/>
+      <c r="J50" s="106" t="s">
+        <v>194</v>
+      </c>
+      <c r="K50" s="5"/>
+      <c r="L50" s="47"/>
+    </row>
+    <row r="51" spans="1:12" ht="62.45">
+      <c r="A51" s="1">
+        <v>21</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C51" s="122" t="str">
+        <f>IF($C$26&gt;0,"Ben Compliance to be checked","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="E51" s="6" t="str">
+        <f>IF($E$26&gt;0,"Ben Compliance to be checked","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="J51" s="101" t="s">
+        <v>195</v>
+      </c>
+      <c r="K51" s="46" t="str">
+        <f ca="1">K6</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L51" s="47"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="1">
+        <v>22</v>
+      </c>
+      <c r="B52" s="5" t="str">
+        <f>J42</f>
+        <v>MGT 8 Applicability</v>
+      </c>
+      <c r="C52" s="122" t="str">
+        <f>$K48</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D52" s="5"/>
+      <c r="E52" s="6" t="str">
+        <f>$L$48</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F52" s="5"/>
+      <c r="J52" s="101"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="47"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="1">
+        <v>23</v>
+      </c>
+      <c r="B53" s="5" t="str">
+        <f>J50</f>
+        <v>Certification of MGT 7</v>
+      </c>
+      <c r="C53" s="122" t="str">
+        <f>$K$53</f>
+        <v>Applicable</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="6" t="str">
+        <f>$L$53</f>
+        <v>Applicable</v>
+      </c>
+      <c r="F53" s="5"/>
+      <c r="J53" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="K53" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="L53" s="50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="A54" s="1">
+        <v>24</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="122" t="str">
+        <f>IF($C$5&gt;100000000,"To appoint KMP","Need not appoint KMP")</f>
+        <v>Need not appoint KMP</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="6" t="str">
+        <f>IF($L$5&gt;100000000,"To appoint KMP","Need not appoint KMP")</f>
+        <v>Need not appoint KMP</v>
+      </c>
+      <c r="F54" s="5"/>
+      <c r="J54" s="45"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="47"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="A55" s="1">
+        <v>25</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C55" s="122" t="str">
+        <f>$O$3</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="E55" s="6" t="str">
+        <f>$P$3</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="J55" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="K55" s="5"/>
+      <c r="L55" s="47"/>
+    </row>
+    <row r="56" spans="1:12">
+      <c r="A56" s="1">
+        <v>26</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C56" s="122" t="str">
+        <f>$O$7</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="E56" s="6" t="str">
+        <f>$P$7</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="J56" s="107" t="s">
+        <v>196</v>
+      </c>
+      <c r="K56" s="46" t="str">
+        <f>IF($C$17&gt;=2000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L56" s="85" t="str">
+        <f>IF($E$17&gt;=2000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="A57" s="1">
+        <v>27</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C57" s="122" t="str">
+        <f>$C$56</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="6" t="str">
+        <f>E56</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F57" s="5"/>
+      <c r="J57" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="K57" s="46" t="str">
+        <f>IF($C$7&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L57" s="85" t="str">
+        <f>IF($E$7&gt;=1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12">
+      <c r="A58" s="1">
+        <v>28</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" s="122" t="str">
+        <f>$C$57</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="6" t="str">
+        <f>E57</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F58" s="5"/>
+      <c r="J58" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="K58" s="46" t="str">
+        <f>IF($C$5&gt;=500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L58" s="47"/>
+    </row>
+    <row r="59" spans="1:12">
+      <c r="A59" s="1">
+        <v>29</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="122" t="str">
+        <f>IF($C$5&gt;250000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="D59" s="5"/>
+      <c r="E59" s="6" t="str">
+        <f>IF($E$5&gt;250000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="F59" s="5"/>
+      <c r="J59" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="K59" s="50" t="str">
+        <f>IF(OR($K$56=$H$3,$K$57=$H$3,$K$58=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L59" s="108" t="str">
+        <f>IF(OR(L56=$H$3,L57=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
+      <c r="D60" s="5"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="5"/>
+      <c r="J60" s="45"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="47"/>
+    </row>
+    <row r="61" spans="1:12">
+      <c r="B61" s="5"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="5"/>
+      <c r="J61" s="48" t="s">
+        <v>164</v>
+      </c>
+      <c r="K61" s="5"/>
+      <c r="L61" s="47"/>
+    </row>
+    <row r="62" spans="1:12">
+      <c r="J62" s="109"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="47"/>
+    </row>
+    <row r="63" spans="1:12">
+      <c r="J63" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="K63" s="5"/>
+      <c r="L63" s="47"/>
+    </row>
+    <row r="64" spans="1:12">
+      <c r="J64" s="51" t="s">
+        <v>230</v>
+      </c>
+      <c r="K64" s="46" t="str">
+        <f>IF(($C$5&gt;=500000000), $H$3, $H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L64" s="46" t="str">
+        <f>IF(($E$5&gt;=500000000), $H$3, $H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="65" spans="10:12">
+      <c r="J65" s="51" t="s">
+        <v>231</v>
+      </c>
+      <c r="K65" s="46" t="str">
+        <f>IF($C$17&gt;=2500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L65" s="46" t="str">
+        <f>IF($E$17&gt;=2500000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="66" spans="10:12">
+      <c r="J66" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="K66" s="46" t="str">
+        <f>IF($C$7&gt;1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L66" s="46" t="str">
+        <f>IF($E$7&gt;1000000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="67" spans="10:12">
+      <c r="J67" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="K67" s="50" t="str">
+        <f>IF(OR($K$63=$H$3,$K$64=$H$3,$K$65=$H$3,$K$66=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L67" s="50" t="str">
+        <f>IF(OR($L$63=$H$3,$L$64=$H$3,$L$65=$H$3,$L$66=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="68" spans="10:12">
+      <c r="J68" s="45"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="47"/>
+    </row>
+    <row r="69" spans="10:12">
+      <c r="J69" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="K69" s="5"/>
+      <c r="L69" s="47"/>
+    </row>
+    <row r="70" spans="10:12">
+      <c r="J70" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L70" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="71" spans="10:12">
+      <c r="J71" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="K71" s="46" t="str">
+        <f>IF($C$5&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L71" s="46" t="str">
+        <f>IF($E$5&gt;=100000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="72" spans="10:12">
+      <c r="J72" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="K72" s="46" t="str">
+        <f>IF($C$5&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L72" s="46" t="str">
+        <f>IF($C$5&gt;=50000000,"Applicable","Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="73" spans="10:12">
+      <c r="J73" s="45"/>
+      <c r="K73" s="46"/>
+      <c r="L73" s="46"/>
+    </row>
+    <row r="74" spans="10:12">
+      <c r="J74" s="99" t="s">
+        <v>80</v>
+      </c>
+      <c r="K74" s="50" t="str">
+        <f>IF(OR($K$70=$H$3,$K$71=$H$3,$K$72=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L74" s="50" t="str">
+        <f>IF(OR($L$70=$H$3,$L$71=$H$3,$L$72=$H$3),$H$3,$H$4)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="75" spans="10:12">
+      <c r="J75" s="45"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="47"/>
+    </row>
+    <row r="76" spans="10:12">
+      <c r="J76" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="K76" s="5"/>
+      <c r="L76" s="47"/>
+    </row>
+    <row r="77" spans="10:12">
+      <c r="J77" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="K77" s="5" t="str">
+        <f>IF(($C$9+$C$10+$C$11)&gt;$H$14,"Check for Shareholders approval","Check for Boards Approval")</f>
+        <v>Check for Boards Approval</v>
+      </c>
+      <c r="L77" s="47" t="str">
+        <f>IF(($E$9+$E$10+$E$11)&gt;$H$14,"Check for Shareholders approval","Check for Boards Approval")</f>
+        <v>Check for Boards Approval</v>
+      </c>
+    </row>
+    <row r="78" spans="10:12">
+      <c r="J78" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="K78" s="5" t="str">
+        <f>IF(($C$9+$C$10+$C$11)&gt;0,$K$77,"Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L78" s="47" t="str">
+        <f>IF(($E$9+$E$10+$E$11)&gt;0,$L$77,"Not Applicable")</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+    <row r="79" spans="10:12">
+      <c r="J79" s="45"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="47"/>
+    </row>
+    <row r="80" spans="10:12">
+      <c r="J80" s="45"/>
+      <c r="K80" s="5"/>
+      <c r="L80" s="47"/>
+    </row>
+    <row r="81" spans="10:12" ht="16.149999999999999" thickBot="1">
+      <c r="J81" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="K81" s="57" t="str">
+        <f>IF(OR(K77=$H$4,K78=$H$4),$H$4,$K$77)</f>
+        <v>Not Applicable</v>
+      </c>
+      <c r="L81" s="87" t="str">
+        <f>IF(OR(L77=$H$4,L78=$H$4),$H$4,$L$77)</f>
+        <v>Not Applicable</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C31">
+    <cfRule type="containsText" dxfId="16" priority="15" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",C31)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K3">
+    <cfRule type="containsText" dxfId="15" priority="13" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K10">
+    <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K10)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20:K22">
+    <cfRule type="containsText" dxfId="13" priority="9" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K51">
+    <cfRule type="containsText" dxfId="12" priority="14" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K51)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K56:K58">
+    <cfRule type="containsText" dxfId="11" priority="8" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K56)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13:L16">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27:L28">
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K27)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K35:L35">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K35)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45:L47">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K45)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K64:L66">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K64)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K71:L73">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",K71)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L20:L21">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L20)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L56:L57">
+    <cfRule type="containsText" dxfId="3" priority="10" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",L56)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O3:P3">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",O3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O7:P7">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",O7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C27 E27" xr:uid="{06BE9F36-F115-483E-99E3-2C9672E0427C}">
+      <formula1>$H$5:$H$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C28 E28" xr:uid="{F6FD8896-A7D2-4FC8-BC7E-FD74CA88C96F}">
+      <formula1>"IND AS, AS"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K13" r:id="rId1" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{CD6D9096-21C7-41EB-BE7B-DEFE9B9FB54E}"/>
+    <hyperlink ref="K14" r:id="rId2" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{FB65852B-961E-4713-81B0-63E9E6A785E0}"/>
+    <hyperlink ref="K15" r:id="rId3" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F926560C-A0F5-43BC-BEF4-25424E8E5F6A}"/>
+    <hyperlink ref="K35" r:id="rId4" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{2215CF82-72FC-45B1-8B60-DB93D8919A15}"/>
+    <hyperlink ref="K46" r:id="rId5" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{25F183C2-CFF4-43C9-ABE3-46FB2D19AEEA}"/>
+    <hyperlink ref="K45" r:id="rId6" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{94658C3B-91E2-4098-ABB0-FBC18982990B}"/>
+    <hyperlink ref="C31" r:id="rId7" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D1190858-75EB-45DB-BC01-023FAD27180A}"/>
+    <hyperlink ref="K51" r:id="rId8" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{4715E62B-A0CA-4689-A080-DC157AEF2953}"/>
+    <hyperlink ref="K56" r:id="rId9" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{FB91505E-1FDB-486A-AA6A-3B45BC3D56A9}"/>
+    <hyperlink ref="K57" r:id="rId10" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{4A77D773-B5F1-4FF4-BA7C-9BB824072ED2}"/>
+    <hyperlink ref="K66" r:id="rId11" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{38D56D50-3DA0-4FDE-BA94-C78F6B24373A}"/>
+    <hyperlink ref="K72" r:id="rId12" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{474B4241-9206-49E3-935F-9B39C78E2587}"/>
+    <hyperlink ref="C39" r:id="rId13" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{C4890AFC-793E-47DB-A1A4-D14C85214FAA}"/>
+    <hyperlink ref="K28" r:id="rId14" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F7B236B7-96C2-4FD2-BE16-E30E91009E85}"/>
+    <hyperlink ref="K27" r:id="rId15" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{85B5165F-544F-4CFA-B020-0309717CE296}"/>
+    <hyperlink ref="C49" r:id="rId16" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A8AFDB6D-53C6-4868-89C8-A5D2B15930CC}"/>
+    <hyperlink ref="L13" r:id="rId17" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{49179C5C-53FD-4555-949F-CC0DAF1569D8}"/>
+    <hyperlink ref="L14" r:id="rId18" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A2FC31B9-8774-4660-8B5E-CFC963BE2D84}"/>
+    <hyperlink ref="L15" r:id="rId19" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A93EB376-21F0-4425-9A23-E76851BD01F7}"/>
+    <hyperlink ref="L35" r:id="rId20" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{FFCBD35B-48B9-4230-9788-B0653E405DCC}"/>
+    <hyperlink ref="L56" r:id="rId21" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{98DEE83F-4FE8-4E8D-999D-C128386AA4E0}"/>
+    <hyperlink ref="L57" r:id="rId22" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{AAB33B50-6923-46E8-8F09-9BE72ECE42E0}"/>
+    <hyperlink ref="K3" r:id="rId23" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{366981C5-3E08-4DA1-AB78-C57628CB7BF2}"/>
+    <hyperlink ref="K20" r:id="rId24" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{80A6446A-38C2-40DE-9081-326E8C2C539A}"/>
+    <hyperlink ref="K21" r:id="rId25" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D9D1BCF7-2B7C-4929-8674-BE04FD0F3727}"/>
+    <hyperlink ref="K64" r:id="rId26" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{36CA4AFC-067B-4F2A-9AF9-D85D49723DA6}"/>
+    <hyperlink ref="K71" r:id="rId27" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A202092B-2F8E-4AAE-BCBE-7E46395160EC}"/>
+    <hyperlink ref="C54" r:id="rId28" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{4EAC33E6-CD80-4771-A31F-306CDC5ED474}"/>
+    <hyperlink ref="O3" r:id="rId29" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{C50DAA51-E6BA-4160-A125-030B85687E3A}"/>
+    <hyperlink ref="O7" r:id="rId30" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{0B0AF87B-8BEF-4E73-9032-0BD04B0FC8DA}"/>
+    <hyperlink ref="C59" r:id="rId31" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D96F8654-1A58-4F47-9562-1EA68303A299}"/>
+    <hyperlink ref="K58" r:id="rId32" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{45372787-54C6-4D61-988C-781CF83E8BB7}"/>
+    <hyperlink ref="K65" r:id="rId33" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{97D79B65-044F-4D3B-8706-E32421E472FA}"/>
+    <hyperlink ref="L20" r:id="rId34" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F76BCF01-DFD5-4E13-930F-950719522A21}"/>
+    <hyperlink ref="L21" r:id="rId35" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{2A7C1AAB-150F-4856-B743-DE24C04E1201}"/>
+    <hyperlink ref="L28" r:id="rId36" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{563796A4-840D-45F7-A6F6-AEC477A1B81B}"/>
+    <hyperlink ref="L27" r:id="rId37" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{4FDCD1E7-B6D6-489D-A58A-EF30EA99F5F6}"/>
+    <hyperlink ref="L46" r:id="rId38" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{A5BD4DD2-A25C-497B-A444-6039F0ADD089}"/>
+    <hyperlink ref="L45" r:id="rId39" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{C83503C7-AF40-43A3-86AF-F53DA9A6909E}"/>
+    <hyperlink ref="L66" r:id="rId40" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{708C3564-B101-4D4A-B29E-FE821416B105}"/>
+    <hyperlink ref="L64" r:id="rId41" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{723AF39D-FA06-4E88-A453-FA4AC18467CE}"/>
+    <hyperlink ref="L65" r:id="rId42" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{6B6FBA72-3EBD-4CD3-964D-C9B988952941}"/>
+    <hyperlink ref="L71" r:id="rId43" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{0D623B1A-2941-41B9-9BA1-417502736E93}"/>
+    <hyperlink ref="L72" r:id="rId44" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{DDC9858A-1BBB-4906-B775-E93CEE5A4FFF}"/>
+    <hyperlink ref="P3" r:id="rId45" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F0C5ABFF-D833-40C0-B05A-19303F76F13F}"/>
+    <hyperlink ref="P7" r:id="rId46" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{DC62F958-5E83-4A65-A9E9-6A8B13F13EAF}"/>
+    <hyperlink ref="E39" r:id="rId47" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{D6392E02-E223-4B47-A3C5-F856A73AFB19}"/>
+    <hyperlink ref="E49" r:id="rId48" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{F83F3CE0-2D19-4295-8F9C-B0D9AB297E14}"/>
+    <hyperlink ref="E54" r:id="rId49" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{45A039AF-CE34-482E-BE24-1B276FD9CEAA}"/>
+    <hyperlink ref="E59" r:id="rId50" display="https://exceljet.net/excel-functions/excel-if-function" xr:uid="{83D93E60-BE59-4F32-A86C-DD57726FFAD4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId51"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BCEAE1-75B7-4EF0-8D8D-1F025F6CF1D4}">
   <dimension ref="B2:G54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="53.6640625" customWidth="1"/>
-    <col min="3" max="3" width="50.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7">
       <c r="B2" s="33" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="C2" s="34" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="46.8" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="46.9">
       <c r="B4" s="30" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="31" t="s">
-        <v>189</v>
+        <v>236</v>
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
     </row>
-    <row r="5" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" ht="15.6">
       <c r="B5" s="30" t="s">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="C5" s="28"/>
       <c r="D5" s="28"/>
@@ -4521,9 +6838,9 @@
       <c r="F5" s="28"/>
       <c r="G5" s="28"/>
     </row>
-    <row r="6" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" ht="15.6">
       <c r="B6" s="30" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="C6" s="29"/>
       <c r="D6" s="28"/>
@@ -4531,9 +6848,9 @@
       <c r="F6" s="28"/>
       <c r="G6" s="28"/>
     </row>
-    <row r="7" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" ht="15.6">
       <c r="B7" s="30" t="s">
-        <v>263</v>
+        <v>239</v>
       </c>
       <c r="C7" s="29"/>
       <c r="D7" s="28"/>
@@ -4541,37 +6858,37 @@
       <c r="F7" s="28"/>
       <c r="G7" s="28"/>
     </row>
-    <row r="8" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B8" s="121" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="121"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
-      <c r="G8" s="121"/>
-    </row>
-    <row r="9" spans="2:7" ht="93.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" ht="15.6">
+      <c r="B8" s="148" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+    </row>
+    <row r="9" spans="2:7" ht="62.45">
       <c r="B9" s="20" t="s">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>193</v>
+        <v>242</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>194</v>
+        <v>243</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>195</v>
+        <v>244</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="15.6">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="10"/>
@@ -4579,15 +6896,15 @@
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" ht="15.6">
       <c r="B11" s="4" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="E11" s="25">
         <f>+C6</f>
@@ -4596,12 +6913,12 @@
       <c r="F11" s="27"/>
       <c r="G11" s="10"/>
     </row>
-    <row r="12" spans="2:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" ht="31.15">
       <c r="B12" s="4" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="D12" s="10"/>
       <c r="E12" s="25">
@@ -4611,12 +6928,12 @@
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
     </row>
-    <row r="13" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" ht="15.6">
       <c r="B13" s="4" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="D13" s="10"/>
       <c r="E13" s="25">
@@ -4626,12 +6943,12 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" ht="15.6">
       <c r="B14" s="4" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="D14" s="10"/>
       <c r="E14" s="25">
@@ -4641,12 +6958,12 @@
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
     </row>
-    <row r="15" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" ht="15.6">
       <c r="B15" s="4" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="D15" s="10"/>
       <c r="E15" s="25">
@@ -4656,12 +6973,12 @@
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" ht="15.6">
       <c r="B16" s="4" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="D16" s="10"/>
       <c r="E16" s="26">
@@ -4671,12 +6988,12 @@
       <c r="F16" s="26"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" ht="15.6">
       <c r="B17" s="4" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="25">
@@ -4686,12 +7003,12 @@
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" ht="15.6">
       <c r="B18" s="4" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="D18" s="10"/>
       <c r="E18" s="25">
@@ -4701,292 +7018,292 @@
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="2:7" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" ht="28.15">
       <c r="B19" s="24" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="23"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="2:7" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" ht="28.15">
       <c r="B20" s="24" t="s">
-        <v>210</v>
+        <v>261</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="23"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7">
       <c r="B24" s="33" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="C24" s="34" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="15.6">
       <c r="B25" s="19" t="s">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="46.8" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="46.9">
       <c r="B26" s="10" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
     </row>
-    <row r="27" spans="2:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" ht="31.15">
       <c r="B27" s="10" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
     </row>
-    <row r="28" spans="2:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:7" ht="31.15">
       <c r="B28" s="20" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="20"/>
     </row>
-    <row r="29" spans="2:7" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:7" ht="31.15">
       <c r="B29" s="10"/>
       <c r="C29" s="4" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
     </row>
-    <row r="30" spans="2:7" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:7" ht="46.9">
       <c r="B30" s="10"/>
       <c r="C30" s="4" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="D30" s="20"/>
       <c r="E30" s="4"/>
     </row>
-    <row r="31" spans="2:7" ht="78" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:7" ht="78">
       <c r="B31" s="10"/>
       <c r="C31" s="21" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="D31" s="20"/>
       <c r="E31" s="4"/>
     </row>
-    <row r="32" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:7" ht="15.6">
       <c r="B32" s="10"/>
-      <c r="C32" s="122" t="s">
-        <v>227</v>
-      </c>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-    </row>
-    <row r="33" spans="2:5" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="C32" s="149" t="s">
+        <v>278</v>
+      </c>
+      <c r="D32" s="149"/>
+      <c r="E32" s="149"/>
+    </row>
+    <row r="33" spans="2:5" ht="93.6">
       <c r="B33" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="C33" s="113" t="s">
-        <v>229</v>
-      </c>
-      <c r="D33" s="113"/>
-      <c r="E33" s="113"/>
-    </row>
-    <row r="34" spans="2:5" ht="30.6" x14ac:dyDescent="0.3">
+        <v>279</v>
+      </c>
+      <c r="C33" s="134" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+    </row>
+    <row r="34" spans="2:5" ht="30.6">
       <c r="B34" s="19" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="D34" s="113"/>
-      <c r="E34" s="113"/>
-    </row>
-    <row r="35" spans="2:5" ht="31.8" x14ac:dyDescent="0.3">
+        <v>282</v>
+      </c>
+      <c r="D34" s="134"/>
+      <c r="E34" s="134"/>
+    </row>
+    <row r="35" spans="2:5" ht="31.9">
       <c r="B35" s="4"/>
       <c r="C35" s="17" t="s">
-        <v>232</v>
-      </c>
-      <c r="D35" s="113"/>
-      <c r="E35" s="113"/>
-    </row>
-    <row r="36" spans="2:5" ht="42" x14ac:dyDescent="0.3">
+        <v>283</v>
+      </c>
+      <c r="D35" s="134"/>
+      <c r="E35" s="134"/>
+    </row>
+    <row r="36" spans="2:5" ht="42">
       <c r="B36" s="4"/>
       <c r="C36" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="D36" s="113"/>
-      <c r="E36" s="113"/>
-    </row>
-    <row r="37" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>284</v>
+      </c>
+      <c r="D36" s="134"/>
+      <c r="E36" s="134"/>
+    </row>
+    <row r="37" spans="2:5" ht="31.15">
       <c r="B37" s="10"/>
-      <c r="C37" s="113" t="s">
-        <v>234</v>
-      </c>
-      <c r="D37" s="113"/>
-      <c r="E37" s="113"/>
-    </row>
-    <row r="38" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C37" s="134" t="s">
+        <v>285</v>
+      </c>
+      <c r="D37" s="134"/>
+      <c r="E37" s="134"/>
+    </row>
+    <row r="38" spans="2:5" ht="31.15">
       <c r="B38" s="10"/>
       <c r="C38" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-    </row>
-    <row r="39" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>286</v>
+      </c>
+      <c r="D38" s="134"/>
+      <c r="E38" s="134"/>
+    </row>
+    <row r="39" spans="2:5" ht="31.15">
       <c r="B39" s="10"/>
       <c r="C39" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D39" s="113"/>
-      <c r="E39" s="113"/>
-    </row>
-    <row r="40" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+      <c r="D39" s="134"/>
+      <c r="E39" s="134"/>
+    </row>
+    <row r="40" spans="2:5" ht="15.6">
       <c r="B40" s="10"/>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="113"/>
-    </row>
-    <row r="41" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C40" s="134"/>
+      <c r="D40" s="134"/>
+      <c r="E40" s="134"/>
+    </row>
+    <row r="41" spans="2:5" ht="15.6">
       <c r="B41" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="113"/>
-      <c r="D41" s="113"/>
-      <c r="E41" s="113"/>
-    </row>
-    <row r="42" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="C41" s="134"/>
+      <c r="D41" s="134"/>
+      <c r="E41" s="134"/>
+    </row>
+    <row r="42" spans="2:5" ht="31.15">
       <c r="B42" s="10"/>
-      <c r="C42" s="113" t="s">
-        <v>238</v>
-      </c>
-      <c r="D42" s="113"/>
-      <c r="E42" s="113"/>
-    </row>
-    <row r="43" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C42" s="134" t="s">
+        <v>289</v>
+      </c>
+      <c r="D42" s="134"/>
+      <c r="E42" s="134"/>
+    </row>
+    <row r="43" spans="2:5" ht="31.15">
       <c r="B43" s="10"/>
       <c r="C43" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="D43" s="113"/>
-      <c r="E43" s="113"/>
-    </row>
-    <row r="44" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>290</v>
+      </c>
+      <c r="D43" s="134"/>
+      <c r="E43" s="134"/>
+    </row>
+    <row r="44" spans="2:5" ht="31.15">
       <c r="B44" s="10"/>
       <c r="C44" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="D44" s="113"/>
-      <c r="E44" s="113"/>
-    </row>
-    <row r="45" spans="2:5" ht="109.2" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+      <c r="D44" s="134"/>
+      <c r="E44" s="134"/>
+    </row>
+    <row r="45" spans="2:5" ht="109.15">
       <c r="B45" s="10"/>
       <c r="C45" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="D45" s="113"/>
-      <c r="E45" s="113"/>
-    </row>
-    <row r="46" spans="2:5" ht="78" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+      <c r="D45" s="134"/>
+      <c r="E45" s="134"/>
+    </row>
+    <row r="46" spans="2:5" ht="78">
       <c r="B46" s="10"/>
-      <c r="C46" s="113" t="s">
-        <v>242</v>
-      </c>
-      <c r="D46" s="113"/>
-      <c r="E46" s="113"/>
-    </row>
-    <row r="47" spans="2:5" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="C46" s="134" t="s">
+        <v>293</v>
+      </c>
+      <c r="D46" s="134"/>
+      <c r="E46" s="134"/>
+    </row>
+    <row r="47" spans="2:5" ht="46.9">
       <c r="B47" s="10"/>
       <c r="C47" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="D47" s="113"/>
-      <c r="E47" s="113"/>
-    </row>
-    <row r="48" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+      <c r="D47" s="134"/>
+      <c r="E47" s="134"/>
+    </row>
+    <row r="48" spans="2:5" ht="31.15">
       <c r="B48" s="14" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>244</v>
+        <v>295</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
     </row>
-    <row r="49" spans="2:5" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" ht="46.9">
       <c r="B49" s="14" t="s">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>246</v>
+        <v>297</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
     </row>
-    <row r="50" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" ht="31.15">
       <c r="B50" s="10"/>
       <c r="C50" s="4" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
     </row>
-    <row r="51" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" ht="31.15">
       <c r="B51" s="10"/>
       <c r="C51" s="4" t="s">
-        <v>248</v>
+        <v>299</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
     </row>
-    <row r="52" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" ht="15.6">
       <c r="B52" s="10"/>
       <c r="C52" s="4" t="s">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
     </row>
-    <row r="53" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" ht="15.6">
       <c r="B53" s="10"/>
       <c r="C53" s="4" t="s">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
     </row>
-    <row r="54" spans="2:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" ht="31.15">
       <c r="B54" s="10"/>
       <c r="C54" s="4" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -5005,74 +7322,83 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FB40D3-76E6-4E2D-97CF-9BEC71240E3A}">
-  <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:D14"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="32.5546875" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" customWidth="1"/>
+    <col min="3" max="3" width="47.140625" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:4">
       <c r="B2" t="s">
-        <v>254</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
       <c r="C3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
       <c r="C4" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
       <c r="C5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
       <c r="C6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
       <c r="C7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+        <v>304</v>
+      </c>
+      <c r="D9" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4">
       <c r="C10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
       <c r="C11" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4">
       <c r="C12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4">
       <c r="C13" t="s">
-        <v>258</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="C14" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
